--- a/Översikt TÖREBODA.xlsx
+++ b/Översikt TÖREBODA.xlsx
@@ -601,7 +601,7 @@
         <v>45587</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44747</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45191</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>44986</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45722</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>46150</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>44900</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45713</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45757</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45727</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45552</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>45264</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>45552</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44608</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>46206</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>44837</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>45632</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>45621</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44937</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>44985</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>45938</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>44964</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>44610</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>46212</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>46274</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45729</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45757</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>45742</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44986</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>44690</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44503</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44684</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44733</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>44726</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>44616</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         <v>44719</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>44614</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>44546</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44503</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>44494</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>44507</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>44719</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>44754</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44532</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>44601</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>44719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>44847</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>44847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>44614</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>44614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44579</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44531</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44852</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>44818</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>44853</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>44858</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>45457</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         <v>45237</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>45443</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         <v>44698</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         <v>45076</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>45552</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45145</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>45245</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         <v>44956</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7178,7 +7178,7 @@
         <v>45373</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>45051</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>45627</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44599</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7548,7 +7548,7 @@
         <v>45077</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>45384</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>45344</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45643</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44664</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45651</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44816</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>45166</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44741</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45309</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45664</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45531</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>45450</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45485</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>45189</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45460</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45460</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45282</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>44988</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>44987</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>44987</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>44901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9169,7 +9169,7 @@
         <v>45099</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9242,7 +9242,7 @@
         <v>45369</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>44749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45457</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>44890</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9544,7 +9544,7 @@
         <v>44950</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>44894</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45627</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44740</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>45096</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45625</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45341</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>45481</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>45350</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44978</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>44924</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10352,7 +10352,7 @@
         <v>45642</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45233</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>44756</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>44860</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         <v>45142</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45888</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>45579</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         <v>45885</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>45885</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>45399</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>45552</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11170,7 +11170,7 @@
         <v>44901</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44924</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11316,7 +11316,7 @@
         <v>45236</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45885</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>44571</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11535,7 +11535,7 @@
         <v>45684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11608,7 +11608,7 @@
         <v>44900</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44964</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>46140</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>44473</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45915</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>45912</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>45803</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>45530</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45919</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45328</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45924</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12416,7 +12416,7 @@
         <v>44978</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12489,7 +12489,7 @@
         <v>45244</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12562,7 +12562,7 @@
         <v>45929</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12635,7 +12635,7 @@
         <v>45443</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12708,7 +12708,7 @@
         <v>44853</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>45145</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>45553</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>46146</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>45082</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>45937</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>45938</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45938</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45405</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>45937</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>45352</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>45268</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>45706</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>45553</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>45349</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13818,7 +13818,7 @@
         <v>45954</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>45555</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13964,7 +13964,7 @@
         <v>46152</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14037,7 +14037,7 @@
         <v>46152</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14110,7 +14110,7 @@
         <v>46152</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>46152</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>46152</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>46152</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>45664</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45954</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>46152</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45961</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45460</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45754</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14840,7 +14840,7 @@
         <v>46152</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14913,7 +14913,7 @@
         <v>45685</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>45665</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15059,7 +15059,7 @@
         <v>45273</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>45971</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>45531</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45972</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45972</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45972</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>45972</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15585,7 +15585,7 @@
         <v>45972</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15663,7 +15663,7 @@
         <v>45974</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45096</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15814,7 +15814,7 @@
         <v>44972</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15887,7 +15887,7 @@
         <v>45627</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>44792</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16033,7 +16033,7 @@
         <v>45156</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>45322</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45373</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16252,7 +16252,7 @@
         <v>44900</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>44868</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>45049</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16471,7 +16471,7 @@
         <v>45750</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>45637</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16617,7 +16617,7 @@
         <v>45191</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>45694</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45133</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>45056</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>46009</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>44987</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>44986</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>46168</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17206,7 +17206,7 @@
         <v>46168</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17284,7 +17284,7 @@
         <v>45699</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>45002</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>44958</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>44923</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>44923</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17649,7 +17649,7 @@
         <v>45556</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44746</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45414</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>44907</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45562</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45700</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45127</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>44937</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45763</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>46057</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>46062</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>46078</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>46085</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>45553</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>44900</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18749,7 +18749,7 @@
         <v>45231</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>45552</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18900,7 +18900,7 @@
         <v>46100</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18973,7 +18973,7 @@
         <v>45425</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19046,7 +19046,7 @@
         <v>46106</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45077</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19197,7 +19197,7 @@
         <v>46111</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19270,7 +19270,7 @@
         <v>44903</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>46100</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>46122</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19489,7 +19489,7 @@
         <v>45448</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19567,7 +19567,7 @@
         <v>44782</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
         <v>46134</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19718,7 +19718,7 @@
         <v>46134</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19791,7 +19791,7 @@
         <v>45246</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>45215</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19937,7 +19937,7 @@
         <v>45750</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20010,7 +20010,7 @@
         <v>45324</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20083,7 +20083,7 @@
         <v>44483</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>46206</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20239,7 +20239,7 @@
         <v>46251</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20317,7 +20317,7 @@
         <v>45531</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45531</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20463,7 +20463,7 @@
         <v>46206</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>44827</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>44827</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>46206</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>46248</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>46248</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45209</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>46210</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45268</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>45328</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44907</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
         <v>44900</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>46248</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>44951</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21515,7 +21515,7 @@
         <v>45757</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21588,7 +21588,7 @@
         <v>46251</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45607</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21739,7 +21739,7 @@
         <v>45142</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21812,7 +21812,7 @@
         <v>44937</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>44697</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>46268</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>46268</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22114,7 +22114,7 @@
         <v>44746</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22187,7 +22187,7 @@
         <v>46268</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>46268</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>46268</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>46268</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>45777</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45581</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22655,7 +22655,7 @@
         <v>46275</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>46231</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>45727</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         <v>46268</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>45713</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>45730</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>45493</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23171,7 +23171,7 @@
         <v>45394</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23244,7 +23244,7 @@
         <v>45439</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>45209</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23390,7 +23390,7 @@
         <v>45631</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>45569</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>45763</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23614,7 +23614,7 @@
         <v>46282</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45593</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>46282</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23833,7 +23833,7 @@
         <v>45811</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45811</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>45569</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45763</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>45831</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45835</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45835</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45841</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45841</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45841</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>45841</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45841</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45841</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>45841</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45764</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>45720</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>45741</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>45720</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>45685</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>45716</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45716</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>46045</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>

--- a/Översikt TÖREBODA.xlsx
+++ b/Översikt TÖREBODA.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE321"/>
+  <dimension ref="A1:AE320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45587</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44747</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45191</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>44986</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>45722</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>46150</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>44900</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>45713</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>46085</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>45757</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>45727</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45552</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>45264</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>45552</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>44608</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>46206</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>44837</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>45166</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>45632</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>45621</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 1591-2023</t>
+          <t>A 7772-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2814,10 +2814,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44937</v>
+        <v>44608</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2830,16 +2830,16 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>10.1</v>
+        <v>2.6</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -2854,7 +2854,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2863,583 +2863,583 @@
         <v>1</v>
       </c>
       <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="W22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1473/artfynd/A 7772-2022 artfynd.xlsx", "A 7772-2022")</f>
+        <v/>
+      </c>
+      <c r="X22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor/A 7772-2022 karta.png", "A 7772-2022")</f>
+        <v/>
+      </c>
+      <c r="Y22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor_geotiff/A 7772-2022 georefererad karta.tif", "A 7772-2022")</f>
+        <v/>
+      </c>
+      <c r="AA22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomål/A 7772-2022 FSC-klagomål.docx", "A 7772-2022")</f>
+        <v/>
+      </c>
+      <c r="AB22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomålsmail/A 7772-2022 FSC-klagomål mail.docx", "A 7772-2022")</f>
+        <v/>
+      </c>
+      <c r="AC22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsyn/A 7772-2022 tillsynsbegäran.docx", "A 7772-2022")</f>
+        <v/>
+      </c>
+      <c r="AD22">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsynsmail/A 7772-2022 tillsynsbegäran mail.docx", "A 7772-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A 1591-2023</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>44937</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>TÖREBODA</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>Grantaggsvamp</t>
         </is>
       </c>
-      <c r="W22">
+      <c r="W23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/artfynd/A 1591-2023 artfynd.xlsx", "A 1591-2023")</f>
         <v/>
       </c>
-      <c r="X22">
+      <c r="X23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor/A 1591-2023 karta.png", "A 1591-2023")</f>
         <v/>
       </c>
-      <c r="Y22">
+      <c r="Y23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor_geotiff/A 1591-2023 georefererad karta.tif", "A 1591-2023")</f>
         <v/>
       </c>
-      <c r="AA22">
+      <c r="AA23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomål/A 1591-2023 FSC-klagomål.docx", "A 1591-2023")</f>
         <v/>
       </c>
-      <c r="AB22">
+      <c r="AB23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomålsmail/A 1591-2023 FSC-klagomål mail.docx", "A 1591-2023")</f>
         <v/>
       </c>
-      <c r="AC22">
+      <c r="AC23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsyn/A 1591-2023 tillsynsbegäran.docx", "A 1591-2023")</f>
         <v/>
       </c>
-      <c r="AD22">
+      <c r="AD23">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsynsmail/A 1591-2023 tillsynsbegäran mail.docx", "A 1591-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="inlineStr">
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>A 9985-2023</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="n">
         <v>44985</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>TÖREBODA</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
+      <c r="E24" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>TÖREBODA</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
         <v>5.5</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>1</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T24" t="n">
         <v>1</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U24" t="n">
         <v>1</v>
       </c>
-      <c r="V23" s="2" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>Revlummer</t>
         </is>
       </c>
-      <c r="W23">
+      <c r="W24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/artfynd/A 9985-2023 artfynd.xlsx", "A 9985-2023")</f>
         <v/>
       </c>
-      <c r="X23">
+      <c r="X24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor/A 9985-2023 karta.png", "A 9985-2023")</f>
         <v/>
       </c>
-      <c r="Y23">
+      <c r="Y24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor_geotiff/A 9985-2023 georefererad karta.tif", "A 9985-2023")</f>
         <v/>
       </c>
-      <c r="AA23">
+      <c r="AA24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomål/A 9985-2023 FSC-klagomål.docx", "A 9985-2023")</f>
         <v/>
       </c>
-      <c r="AB23">
+      <c r="AB24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomålsmail/A 9985-2023 FSC-klagomål mail.docx", "A 9985-2023")</f>
         <v/>
       </c>
-      <c r="AC23">
+      <c r="AC24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsyn/A 9985-2023 tillsynsbegäran.docx", "A 9985-2023")</f>
         <v/>
       </c>
-      <c r="AD23">
+      <c r="AD24">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsynsmail/A 9985-2023 tillsynsbegäran mail.docx", "A 9985-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="inlineStr">
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>A 49169-2025</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="n">
         <v>45938</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>TÖREBODA</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
+      <c r="E25" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>TÖREBODA</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
         <v>4.5</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>1</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T25" t="n">
         <v>1</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>Havsörn</t>
         </is>
       </c>
-      <c r="W24">
+      <c r="W25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/artfynd/A 49169-2025 artfynd.xlsx", "A 49169-2025")</f>
         <v/>
       </c>
-      <c r="X24">
+      <c r="X25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor/A 49169-2025 karta.png", "A 49169-2025")</f>
         <v/>
       </c>
-      <c r="Y24">
+      <c r="Y25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor_geotiff/A 49169-2025 georefererad karta.tif", "A 49169-2025")</f>
         <v/>
       </c>
-      <c r="AA24">
+      <c r="AA25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomål/A 49169-2025 FSC-klagomål.docx", "A 49169-2025")</f>
         <v/>
       </c>
-      <c r="AB24">
+      <c r="AB25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomålsmail/A 49169-2025 FSC-klagomål mail.docx", "A 49169-2025")</f>
         <v/>
       </c>
-      <c r="AC24">
+      <c r="AC25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsyn/A 49169-2025 tillsynsbegäran.docx", "A 49169-2025")</f>
         <v/>
       </c>
-      <c r="AD24">
+      <c r="AD25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsynsmail/A 49169-2025 tillsynsbegäran mail.docx", "A 49169-2025")</f>
         <v/>
       </c>
-      <c r="AE24">
+      <c r="AE25">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/fåglar/A 49169-2025 prioriterade fågelarter.docx", "A 49169-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="inlineStr">
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>A 6160-2023</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="n">
         <v>44964</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>TÖREBODA</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
+      <c r="E26" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>TÖREBODA</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>1.6</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U26" t="n">
         <v>1</v>
       </c>
-      <c r="V25" s="2" t="inlineStr">
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>Havsörn</t>
         </is>
       </c>
-      <c r="W25">
+      <c r="W26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/artfynd/A 6160-2023 artfynd.xlsx", "A 6160-2023")</f>
         <v/>
       </c>
-      <c r="X25">
+      <c r="X26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor/A 6160-2023 karta.png", "A 6160-2023")</f>
         <v/>
       </c>
-      <c r="Y25">
+      <c r="Y26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor_geotiff/A 6160-2023 georefererad karta.tif", "A 6160-2023")</f>
         <v/>
       </c>
-      <c r="AA25">
+      <c r="AA26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomål/A 6160-2023 FSC-klagomål.docx", "A 6160-2023")</f>
         <v/>
       </c>
-      <c r="AB25">
+      <c r="AB26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomålsmail/A 6160-2023 FSC-klagomål mail.docx", "A 6160-2023")</f>
         <v/>
       </c>
-      <c r="AC25">
+      <c r="AC26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsyn/A 6160-2023 tillsynsbegäran.docx", "A 6160-2023")</f>
         <v/>
       </c>
-      <c r="AD25">
+      <c r="AD26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsynsmail/A 6160-2023 tillsynsbegäran mail.docx", "A 6160-2023")</f>
         <v/>
       </c>
-      <c r="AE25">
+      <c r="AE26">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/fåglar/A 6160-2023 prioriterade fågelarter.docx", "A 6160-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>A 8266-2022</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
         <v>44610</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>TÖREBODA</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="E27" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>VÄSTRA GÖTALANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>TÖREBODA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>0.5</v>
       </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>1</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U27" t="n">
         <v>1</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>Dofttaggsvamp</t>
         </is>
       </c>
-      <c r="W26">
+      <c r="W27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/artfynd/A 8266-2022 artfynd.xlsx", "A 8266-2022")</f>
         <v/>
       </c>
-      <c r="X26">
+      <c r="X27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor/A 8266-2022 karta.png", "A 8266-2022")</f>
         <v/>
       </c>
-      <c r="Y26">
+      <c r="Y27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor_geotiff/A 8266-2022 georefererad karta.tif", "A 8266-2022")</f>
         <v/>
       </c>
-      <c r="AA26">
+      <c r="AA27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomål/A 8266-2022 FSC-klagomål.docx", "A 8266-2022")</f>
         <v/>
       </c>
-      <c r="AB26">
+      <c r="AB27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomålsmail/A 8266-2022 FSC-klagomål mail.docx", "A 8266-2022")</f>
         <v/>
       </c>
-      <c r="AC26">
+      <c r="AC27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsyn/A 8266-2022 tillsynsbegäran.docx", "A 8266-2022")</f>
         <v/>
       </c>
-      <c r="AD26">
+      <c r="AD27">
         <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsynsmail/A 8266-2022 tillsynsbegäran mail.docx", "A 8266-2022")</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 7772-2022</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>44608</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>TÖREBODA</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1473/artfynd/A 7772-2022 artfynd.xlsx", "A 7772-2022")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor/A 7772-2022 karta.png", "A 7772-2022")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1473/kartor_geotiff/A 7772-2022 georefererad karta.tif", "A 7772-2022")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomål/A 7772-2022 FSC-klagomål.docx", "A 7772-2022")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1473/klagomålsmail/A 7772-2022 FSC-klagomål mail.docx", "A 7772-2022")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsyn/A 7772-2022 tillsynsbegäran.docx", "A 7772-2022")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1473/tillsynsmail/A 7772-2022 tillsynsbegäran mail.docx", "A 7772-2022")</f>
-        <v/>
-      </c>
-    </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>46212</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>46274</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>45729</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         <v>45757</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>45742</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         <v>44986</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>44690</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44509</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>44503</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44684</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>44733</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>44740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>44818</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>44726</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>44616</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 23024-2022</t>
+          <t>A 8915-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4950,10 +4950,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44719</v>
+        <v>44614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4965,8 +4965,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.1</v>
+        <v>18.4</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -5009,7 +5014,7 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 8915-2022</t>
+          <t>A 23024-2022</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5023,10 +5028,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44614</v>
+        <v>44719</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5038,13 +5043,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>18.4</v>
+        <v>0.1</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5104,7 +5104,7 @@
         <v>44546</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>44503</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         <v>44494</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
         <v>44507</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>44719</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>44754</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44532</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5620,7 +5620,7 @@
         <v>44601</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>44719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>44847</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>44847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>44614</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         <v>44614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44579</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>44531</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>44852</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>44818</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 47322-2022</t>
+          <t>A 24363-2024</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6362,10 +6362,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44853</v>
+        <v>45457</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6379,11 +6379,11 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -6426,7 +6426,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 48491-2022</t>
+          <t>A 22021-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6440,10 +6440,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44858</v>
+        <v>45443</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -6499,7 +6499,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 24363-2024</t>
+          <t>A 24381-2023</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6513,10 +6513,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45457</v>
+        <v>45076</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6528,13 +6528,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.1</v>
+        <v>4.4</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -6577,7 +6572,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 55285-2023</t>
+          <t>A 20210-2022</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6591,10 +6586,10 @@
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45237</v>
+        <v>44698</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6607,7 +6602,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -6650,7 +6645,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 22021-2024</t>
+          <t>A 39652-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6664,10 +6659,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45443</v>
+        <v>45552</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6680,7 +6675,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -6723,7 +6718,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 20210-2022</t>
+          <t>A 35238-2023</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6737,10 +6732,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44698</v>
+        <v>45145</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6753,7 +6748,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -6796,7 +6791,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 24381-2023</t>
+          <t>A 11680-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6806,14 +6801,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45076</v>
+        <v>45373</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6826,7 +6821,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4.4</v>
+        <v>12.3</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -6869,7 +6864,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 39652-2024</t>
+          <t>A 57220-2023</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6883,10 +6878,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45552</v>
+        <v>45245</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6899,7 +6894,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -6942,7 +6937,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35238-2023</t>
+          <t>A 4435-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6956,10 +6951,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45145</v>
+        <v>44956</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6972,7 +6967,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7015,7 +7010,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 57220-2023</t>
+          <t>A 47322-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7029,10 +7024,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45245</v>
+        <v>44853</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7044,8 +7039,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7088,7 +7088,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 4435-2023</t>
+          <t>A 48491-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7102,10 +7102,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44956</v>
+        <v>44858</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7161,7 +7161,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 11680-2024</t>
+          <t>A 19723-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7171,14 +7171,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45373</v>
+        <v>45051</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7190,8 +7190,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>12.3</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -7234,7 +7239,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 19723-2023</t>
+          <t>A 56685-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -7248,10 +7253,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45051</v>
+        <v>45627</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7263,13 +7268,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -7312,7 +7312,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 56685-2024</t>
+          <t>A 6446-2025</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -7322,14 +7322,14 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45627</v>
+        <v>45699</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7342,7 +7342,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -7385,7 +7385,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 6446-2025</t>
+          <t>A 5971-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -7395,14 +7395,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45699</v>
+        <v>44599</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -7458,7 +7458,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 5971-2022</t>
+          <t>A 23664-2023</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -7472,10 +7472,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44599</v>
+        <v>45077</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7487,8 +7487,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -7531,7 +7536,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 23664-2023</t>
+          <t>A 55285-2023</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -7545,10 +7550,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45077</v>
+        <v>45237</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7560,13 +7565,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -7626,7 +7626,7 @@
         <v>45384</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>45344</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7772,7 +7772,7 @@
         <v>45643</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>44664</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>45651</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44816</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         <v>45166</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44741</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45309</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>45664</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45531</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>45450</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45485</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 44518-2023</t>
+          <t>A 24544-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8582,10 +8582,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45189</v>
+        <v>45460</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.8</v>
+        <v>7.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -8641,7 +8641,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 24544-2024</t>
+          <t>A 24546-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8658,7 +8658,7 @@
         <v>45460</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7.3</v>
+        <v>5.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -8714,7 +8714,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 24546-2024</t>
+          <t>A 64799-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8728,10 +8728,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45460</v>
+        <v>45282</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -8787,7 +8787,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 64799-2023</t>
+          <t>A 10598-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8801,10 +8801,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45282</v>
+        <v>44988</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -8860,7 +8860,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 10598-2023</t>
+          <t>A 10430-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>44988</v>
+        <v>44987</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 10430-2023</t>
+          <t>A 10431-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8950,7 +8950,7 @@
         <v>44987</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9006,7 +9006,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 10431-2023</t>
+          <t>A 58226-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>44987</v>
+        <v>44901</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9079,7 +9079,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 58226-2022</t>
+          <t>A 10833-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9093,10 +9093,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44901</v>
+        <v>45369</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -9169,7 +9169,7 @@
         <v>45099</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 10833-2024</t>
+          <t>A 28965-2022</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9239,10 +9239,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45369</v>
+        <v>44749</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 28965-2022</t>
+          <t>A 27231-2023</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9312,10 +9312,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>44749</v>
+        <v>45096</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9325,6 +9325,11 @@
       <c r="G104" t="inlineStr">
         <is>
           <t>TÖREBODA</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -9371,7 +9376,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 24355-2024</t>
+          <t>A 56273-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9385,10 +9390,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45457</v>
+        <v>44890</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9406,7 +9411,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>12.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -9449,7 +9454,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 56273-2022</t>
+          <t>A 3508-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9463,10 +9468,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44890</v>
+        <v>44950</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9478,13 +9483,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>12.6</v>
+        <v>2.1</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -9527,7 +9527,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 3508-2023</t>
+          <t>A 26759-2022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9541,10 +9541,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>44950</v>
+        <v>44740</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -9600,7 +9600,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 56831-2022</t>
+          <t>A 56614-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9610,14 +9610,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>44894</v>
+        <v>45625</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -9673,7 +9673,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 56684-2024</t>
+          <t>A 24355-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9687,10 +9687,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45627</v>
+        <v>45457</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9702,8 +9702,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I109" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -9746,7 +9751,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 26759-2022</t>
+          <t>A 10448-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9760,10 +9765,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>44740</v>
+        <v>45720</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9776,7 +9781,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -9819,7 +9824,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 27231-2023</t>
+          <t>A 56831-2022</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9829,14 +9834,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45096</v>
+        <v>44894</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9846,11 +9851,6 @@
       <c r="G111" t="inlineStr">
         <is>
           <t>TÖREBODA</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -9897,7 +9897,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 56614-2024</t>
+          <t>A 56684-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9911,10 +9911,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45625</v>
+        <v>45627</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9970,7 +9970,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 6578-2024</t>
+          <t>A 38987-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9984,10 +9984,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45341</v>
+        <v>45888</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10043,7 +10043,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 29023-2024</t>
+          <t>A 60267-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10057,10 +10057,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45481</v>
+        <v>45642</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10073,7 +10073,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -10116,7 +10116,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 8315-2024</t>
+          <t>A 16265-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10130,10 +10130,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45350</v>
+        <v>45750</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -10189,7 +10189,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 9655-2023</t>
+          <t>A 6578-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10203,10 +10203,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44978</v>
+        <v>45341</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.5</v>
+        <v>5.3</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -10262,7 +10262,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 62521-2022</t>
+          <t>A 29023-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10276,10 +10276,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>44924</v>
+        <v>45481</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10292,7 +10292,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -10335,7 +10335,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 60267-2024</t>
+          <t>A 8315-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10349,10 +10349,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45642</v>
+        <v>45350</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -10408,7 +10408,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 54459-2023</t>
+          <t>A 9655-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10422,10 +10422,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45233</v>
+        <v>44978</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10437,13 +10437,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -10486,7 +10481,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 29891-2022</t>
+          <t>A 38705-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10500,10 +10495,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44756</v>
+        <v>45885</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10516,7 +10511,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -10559,7 +10554,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 48957-2022</t>
+          <t>A 38706-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10573,10 +10568,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44860</v>
+        <v>45885</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10588,13 +10583,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -10637,7 +10627,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 34865-2023</t>
+          <t>A 62521-2022</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10651,10 +10641,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45142</v>
+        <v>44924</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10666,13 +10656,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -10715,7 +10700,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 38987-2025</t>
+          <t>A 989-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -10729,10 +10714,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45888</v>
+        <v>44571</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10745,7 +10730,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -10788,7 +10773,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 45649-2024</t>
+          <t>A 54459-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -10802,10 +10787,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45579</v>
+        <v>45233</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10817,8 +10802,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -10861,7 +10851,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 38705-2025</t>
+          <t>A 29891-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -10875,10 +10865,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45885</v>
+        <v>44756</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10891,7 +10881,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -10934,7 +10924,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 38706-2025</t>
+          <t>A 38704-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -10951,7 +10941,7 @@
         <v>45885</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10964,7 +10954,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>1.2</v>
+        <v>4.5</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11007,7 +10997,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 15086-2024</t>
+          <t>A 4109-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11021,10 +11011,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45399</v>
+        <v>45684</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11037,7 +11027,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -11080,7 +11070,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 39621-2024</t>
+          <t>A 44074-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11094,10 +11084,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45552</v>
+        <v>45915</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11110,7 +11100,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.7</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -11153,7 +11143,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 58213-2022</t>
+          <t>A 48957-2022</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11167,10 +11157,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44901</v>
+        <v>44860</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11182,8 +11172,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -11226,7 +11221,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 62542-2022</t>
+          <t>A 43688-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11240,10 +11235,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44924</v>
+        <v>45912</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11256,7 +11251,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.5</v>
+        <v>3.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -11299,7 +11294,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 54734-2023</t>
+          <t>A 25908-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11313,10 +11308,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45236</v>
+        <v>45803</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11329,7 +11324,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -11372,7 +11367,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 38704-2025</t>
+          <t>A 45262-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11386,10 +11381,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45885</v>
+        <v>45919</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11402,7 +11397,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -11445,7 +11440,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 989-2022</t>
+          <t>A 34865-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11459,10 +11454,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44571</v>
+        <v>45142</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11474,8 +11469,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 4109-2025</t>
+          <t>A 46135-2025</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11532,10 +11532,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45684</v>
+        <v>45924</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -11591,7 +11591,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 58123-2022</t>
+          <t>A 45649-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11605,10 +11605,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44900</v>
+        <v>45579</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -11664,7 +11664,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 6162-2023</t>
+          <t>A 15086-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11678,10 +11678,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44964</v>
+        <v>45399</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.5</v>
+        <v>3.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -11737,7 +11737,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 20471-2026</t>
+          <t>A 46972-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11751,10 +11751,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46140</v>
+        <v>45929</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11766,13 +11766,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -11815,7 +11810,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 54621-2021</t>
+          <t>A 39621-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11829,10 +11824,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44473</v>
+        <v>45552</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11845,7 +11840,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>6.4</v>
+        <v>3.7</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -11888,7 +11883,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 44074-2025</t>
+          <t>A 58213-2022</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11902,10 +11897,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45915</v>
+        <v>44901</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11918,7 +11913,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -11961,7 +11956,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 43688-2025</t>
+          <t>A 62542-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11975,10 +11970,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45912</v>
+        <v>44924</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11991,7 +11986,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3.8</v>
+        <v>0.5</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -12034,7 +12029,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 25908-2025</t>
+          <t>A 20471-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -12048,10 +12043,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45803</v>
+        <v>46140</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12063,8 +12058,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -12107,7 +12107,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 35232-2024</t>
+          <t>A 54621-2021</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -12121,10 +12121,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45530</v>
+        <v>44473</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>6.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -12180,7 +12180,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 45262-2025</t>
+          <t>A 54734-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -12194,10 +12194,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45919</v>
+        <v>45236</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12210,7 +12210,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -12253,7 +12253,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 4708-2024</t>
+          <t>A 49088-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -12267,10 +12267,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45328</v>
+        <v>45937</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12282,8 +12282,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I144" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -12326,7 +12331,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 46135-2025</t>
+          <t>A 49171-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -12340,10 +12345,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45924</v>
+        <v>45938</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12356,7 +12361,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -12399,7 +12404,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 9651-2023</t>
+          <t>A 49177-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -12413,10 +12418,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44978</v>
+        <v>45938</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12429,7 +12434,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>2.8</v>
+        <v>6.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -12472,7 +12477,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 56805-2023</t>
+          <t>A 21187-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -12486,10 +12491,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45244</v>
+        <v>46146</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12502,7 +12507,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -12545,7 +12550,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 46972-2025</t>
+          <t>A 49085-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -12559,10 +12564,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45929</v>
+        <v>45937</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12574,8 +12579,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -12618,7 +12628,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 22048-2024</t>
+          <t>A 21966-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -12632,10 +12642,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45443</v>
+        <v>46152</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12648,7 +12658,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.5</v>
+        <v>8.6</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -12691,7 +12701,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 47319-2022</t>
+          <t>A 21967-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -12705,10 +12715,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44853</v>
+        <v>46152</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12720,13 +12730,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>2.6</v>
+        <v>0.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -12769,7 +12774,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 35239-2023</t>
+          <t>A 21968-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -12783,10 +12788,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45145</v>
+        <v>46152</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12799,7 +12804,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -12842,7 +12847,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 39798-2024</t>
+          <t>A 21961-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -12856,10 +12861,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45553</v>
+        <v>46152</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12872,7 +12877,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -12915,7 +12920,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 21187-2026</t>
+          <t>A 21962-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -12929,10 +12934,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46146</v>
+        <v>46152</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12945,7 +12950,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -12988,7 +12993,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 24349-2023</t>
+          <t>A 21965-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -13002,10 +13007,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45082</v>
+        <v>46152</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13018,7 +13023,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -13061,7 +13066,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 49088-2025</t>
+          <t>A 21964-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -13075,10 +13080,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45937</v>
+        <v>46152</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13090,13 +13095,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -13139,7 +13139,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 49171-2025</t>
+          <t>A 21963-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -13153,10 +13153,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45938</v>
+        <v>46152</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>4.8</v>
+        <v>0.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -13212,7 +13212,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 49177-2025</t>
+          <t>A 1981-2025</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -13226,10 +13226,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45938</v>
+        <v>45665</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>6.9</v>
+        <v>1.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -13285,7 +13285,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 16007-2024</t>
+          <t>A 58123-2022</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -13299,10 +13299,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45405</v>
+        <v>44900</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13315,7 +13315,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -13358,7 +13358,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 49085-2025</t>
+          <t>A 6162-2023</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -13372,10 +13372,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45937</v>
+        <v>44964</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13387,13 +13387,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>4.1</v>
+        <v>0.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -13436,7 +13431,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 8402-2024</t>
+          <t>A 35232-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -13450,10 +13445,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45352</v>
+        <v>45530</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13466,7 +13461,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -13509,7 +13504,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 62782-2023</t>
+          <t>A 4708-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -13523,10 +13518,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45268</v>
+        <v>45328</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13539,7 +13534,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>2.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -13582,7 +13577,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 7676-2025</t>
+          <t>A 52638-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -13596,10 +13591,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45706</v>
+        <v>45954</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13612,7 +13607,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -13655,7 +13650,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 39797-2024</t>
+          <t>A 52639-2025</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -13669,10 +13664,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45553</v>
+        <v>45954</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13685,7 +13680,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -13728,7 +13723,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 7826-2024</t>
+          <t>A 9651-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -13742,10 +13737,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45349</v>
+        <v>44978</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13758,7 +13753,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -13801,7 +13796,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 52638-2025</t>
+          <t>A 56805-2023</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -13815,10 +13810,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45954</v>
+        <v>45244</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13831,7 +13826,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -13874,7 +13869,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 40542-2024</t>
+          <t>A 54016-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -13888,10 +13883,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45555</v>
+        <v>45961</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13904,7 +13899,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -13947,7 +13942,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 21966-2026</t>
+          <t>A 22048-2024</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -13961,10 +13956,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46152</v>
+        <v>45443</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13977,7 +13972,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>8.6</v>
+        <v>2.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -14020,7 +14015,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 21967-2026</t>
+          <t>A 47319-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -14034,10 +14029,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46152</v>
+        <v>44853</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14049,8 +14044,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>0.6</v>
+        <v>2.6</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -14093,7 +14093,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 21968-2026</t>
+          <t>A 35239-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -14107,10 +14107,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46152</v>
+        <v>45145</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.7</v>
+        <v>0.8</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -14166,7 +14166,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 21961-2026</t>
+          <t>A 55593-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -14176,14 +14176,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46152</v>
+        <v>45971</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>0.8</v>
+        <v>20.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -14239,7 +14239,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 21962-2026</t>
+          <t>A 39798-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -14253,10 +14253,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46152</v>
+        <v>45553</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -14312,7 +14312,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 21965-2026</t>
+          <t>A 24349-2023</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -14326,10 +14326,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46152</v>
+        <v>45082</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -14385,7 +14385,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 907-2025</t>
+          <t>A 55729-2025</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -14399,10 +14399,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45664</v>
+        <v>45972</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -14458,7 +14458,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 52639-2025</t>
+          <t>A 55652-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -14472,10 +14472,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45954</v>
+        <v>45972</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14487,8 +14487,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -14531,7 +14536,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 21964-2026</t>
+          <t>A 55656-2025</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -14545,10 +14550,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46152</v>
+        <v>45972</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14560,8 +14565,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>8.699999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -14604,7 +14614,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 54016-2025</t>
+          <t>A 55766-2025</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -14614,14 +14624,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45961</v>
+        <v>45972</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14633,8 +14643,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -14677,7 +14692,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 24545-2024</t>
+          <t>A 55648-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -14691,10 +14706,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45460</v>
+        <v>45972</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14706,8 +14721,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -14750,7 +14770,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 16703-2025</t>
+          <t>A 59315-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -14764,10 +14784,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45754</v>
+        <v>45637</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14780,7 +14800,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -14823,7 +14843,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 21963-2026</t>
+          <t>A 56131-2025</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -14837,10 +14857,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46152</v>
+        <v>45974</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14853,7 +14873,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.4</v>
+        <v>6.3</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -14896,7 +14916,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 4300-2025</t>
+          <t>A 16007-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -14910,10 +14930,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45685</v>
+        <v>45405</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14926,7 +14946,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -14969,7 +14989,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 1981-2025</t>
+          <t>A 45161-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -14983,10 +15003,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45665</v>
+        <v>45191</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14999,7 +15019,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -15042,7 +15062,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 63113-2023</t>
+          <t>A 8402-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -15056,10 +15076,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45273</v>
+        <v>45352</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15072,7 +15092,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -15115,7 +15135,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 55593-2025</t>
+          <t>A 62782-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -15125,14 +15145,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45971</v>
+        <v>45268</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15145,7 +15165,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>20.8</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -15188,7 +15208,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 35487-2024</t>
+          <t>A 7676-2025</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -15202,10 +15222,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45531</v>
+        <v>45706</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15218,7 +15238,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -15261,7 +15281,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 55729-2025</t>
+          <t>A 24160-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -15275,10 +15295,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45972</v>
+        <v>46168</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15290,8 +15310,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -15334,7 +15359,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 55652-2025</t>
+          <t>A 24161-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -15348,10 +15373,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45972</v>
+        <v>46168</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15369,7 +15394,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -15412,7 +15437,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 55656-2025</t>
+          <t>A 39797-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -15426,10 +15451,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45972</v>
+        <v>45553</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15441,13 +15466,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>5.7</v>
+        <v>1.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -15490,7 +15510,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 55766-2025</t>
+          <t>A 7826-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -15500,14 +15520,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45972</v>
+        <v>45349</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15519,13 +15539,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -15568,7 +15583,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 55648-2025</t>
+          <t>A 40542-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -15582,10 +15597,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45972</v>
+        <v>45555</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15597,13 +15612,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -15646,7 +15656,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 56131-2025</t>
+          <t>A 907-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -15660,10 +15670,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45974</v>
+        <v>45664</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15676,7 +15686,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>6.3</v>
+        <v>1.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -15719,7 +15729,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 27251-2023</t>
+          <t>A 24545-2024</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -15733,10 +15743,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45096</v>
+        <v>45460</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15748,13 +15758,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -15797,7 +15802,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 7680-2023</t>
+          <t>A 16703-2025</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -15811,10 +15816,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44972</v>
+        <v>45754</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15827,7 +15832,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>7.4</v>
+        <v>2.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -15870,7 +15875,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 56682-2024</t>
+          <t>A 1554-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -15884,10 +15889,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45627</v>
+        <v>44937</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15899,8 +15904,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -15943,7 +15953,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 34436-2022</t>
+          <t>A 4300-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -15957,10 +15967,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44792</v>
+        <v>45685</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15973,7 +15983,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -16016,7 +16026,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 37837-2023</t>
+          <t>A 63113-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -16030,10 +16040,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45156</v>
+        <v>45273</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16046,7 +16056,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -16089,7 +16099,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 3968-2024</t>
+          <t>A 35487-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -16103,10 +16113,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45322</v>
+        <v>45531</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16119,7 +16129,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -16162,7 +16172,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 11683-2024</t>
+          <t>A 62980-2025</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -16172,14 +16182,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45373</v>
+        <v>46009</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16192,7 +16202,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>23.8</v>
+        <v>3.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -16235,7 +16245,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 57984-2022</t>
+          <t>A 27251-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -16249,10 +16259,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44900</v>
+        <v>45096</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16264,8 +16274,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -16308,7 +16323,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 51040-2022</t>
+          <t>A 7680-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -16322,10 +16337,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>44868</v>
+        <v>44972</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16338,7 +16353,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -16381,7 +16396,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 19256-2023</t>
+          <t>A 56682-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -16395,10 +16410,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45049</v>
+        <v>45627</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16411,7 +16426,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -16454,7 +16469,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 16267-2025</t>
+          <t>A 34436-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -16468,10 +16483,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45750</v>
+        <v>44792</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16484,7 +16499,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.5</v>
+        <v>4.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -16527,7 +16542,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 59315-2024</t>
+          <t>A 37837-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -16541,10 +16556,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45637</v>
+        <v>45156</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16557,7 +16572,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -16600,7 +16615,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 45161-2023</t>
+          <t>A 3968-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -16614,10 +16629,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45191</v>
+        <v>45322</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16630,7 +16645,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -16673,7 +16688,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 5819-2025</t>
+          <t>A 11683-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -16683,14 +16698,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45694</v>
+        <v>45373</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16703,7 +16718,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.7</v>
+        <v>23.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -16746,7 +16761,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 33754-2023</t>
+          <t>A 57984-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -16760,10 +16775,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45133</v>
+        <v>44900</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16776,7 +16791,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -16819,7 +16834,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 20391-2023</t>
+          <t>A 51040-2022</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -16833,10 +16848,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45056</v>
+        <v>44868</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16849,7 +16864,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>6.5</v>
+        <v>1.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -16892,7 +16907,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 62980-2025</t>
+          <t>A 19256-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -16906,10 +16921,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46009</v>
+        <v>45049</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16922,7 +16937,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -16965,7 +16980,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 11159-2023</t>
+          <t>A 16267-2025</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -16979,10 +16994,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44987</v>
+        <v>45750</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16995,7 +17010,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -17038,7 +17053,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 10185-2023</t>
+          <t>A 6970-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -17052,10 +17067,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44986</v>
+        <v>46057</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17068,7 +17083,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -17111,7 +17126,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 24160-2026</t>
+          <t>A 7860-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -17125,10 +17140,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46168</v>
+        <v>46062</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17140,13 +17155,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1.2</v>
+        <v>3.9</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -17189,7 +17199,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 24161-2026</t>
+          <t>A 5819-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -17203,10 +17213,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46168</v>
+        <v>45694</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17218,13 +17228,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -17267,7 +17272,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 6442-2025</t>
+          <t>A 33754-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -17277,14 +17282,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45699</v>
+        <v>45133</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17297,7 +17302,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -17340,7 +17345,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 13056-2023</t>
+          <t>A 20391-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -17354,10 +17359,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45002</v>
+        <v>45056</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17370,7 +17375,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.1</v>
+        <v>6.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -17413,7 +17418,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 4941-2023</t>
+          <t>A 10818-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -17427,10 +17432,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>44958</v>
+        <v>46078</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17443,7 +17448,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -17486,7 +17491,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 62359-2022</t>
+          <t>A 11159-2023</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -17500,10 +17505,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44923</v>
+        <v>44987</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17516,7 +17521,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -17559,7 +17564,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 62363-2022</t>
+          <t>A 10185-2023</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -17573,10 +17578,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>44923</v>
+        <v>44986</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17589,7 +17594,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -17632,7 +17637,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 40598-2024</t>
+          <t>A 6442-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -17642,14 +17647,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45556</v>
+        <v>45699</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17662,7 +17667,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -17705,7 +17710,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 28183-2022</t>
+          <t>A 11863-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -17719,10 +17724,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44746</v>
+        <v>46085</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17735,7 +17740,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -17778,7 +17783,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 17360-2024</t>
+          <t>A 13056-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -17792,10 +17797,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45414</v>
+        <v>45002</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17808,7 +17813,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -17851,7 +17856,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 59440-2022</t>
+          <t>A 4941-2023</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -17865,10 +17870,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44907</v>
+        <v>44958</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17881,7 +17886,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -17924,7 +17929,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 42109-2024</t>
+          <t>A 62359-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -17938,10 +17943,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45562</v>
+        <v>44923</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17954,7 +17959,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -17997,7 +18002,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 6811-2025</t>
+          <t>A 62363-2022</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -18011,10 +18016,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45700</v>
+        <v>44923</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18027,7 +18032,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>7.1</v>
+        <v>0.4</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -18070,7 +18075,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 33276-2023</t>
+          <t>A 40598-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -18084,10 +18089,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45127</v>
+        <v>45556</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18100,7 +18105,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -18143,7 +18148,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 1554-2023</t>
+          <t>A 28183-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -18157,10 +18162,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>44937</v>
+        <v>44746</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18172,13 +18177,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -18221,7 +18221,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 18687-2025</t>
+          <t>A 14557-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -18235,10 +18235,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45763</v>
+        <v>46100</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -18294,7 +18294,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 6970-2026</t>
+          <t>A 17360-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -18308,10 +18308,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>46057</v>
+        <v>45414</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -18367,7 +18367,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 7860-2026</t>
+          <t>A 59440-2022</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -18381,10 +18381,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46062</v>
+        <v>44907</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -18440,7 +18440,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 10818-2026</t>
+          <t>A 42109-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -18454,10 +18454,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46078</v>
+        <v>45562</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.6</v>
+        <v>6.2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -18513,7 +18513,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 11863-2026</t>
+          <t>A 15567-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -18523,14 +18523,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46085</v>
+        <v>46106</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>3.2</v>
+        <v>5.7</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -18586,7 +18586,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 39791-2024</t>
+          <t>A 6811-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -18600,10 +18600,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45553</v>
+        <v>45700</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3.8</v>
+        <v>7.1</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -18659,7 +18659,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 58013-2022</t>
+          <t>A 16200-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -18673,10 +18673,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44900</v>
+        <v>46111</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -18732,7 +18732,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 53791-2023</t>
+          <t>A 33276-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -18746,10 +18746,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45231</v>
+        <v>45127</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18761,13 +18761,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -18810,7 +18805,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 39660-2024</t>
+          <t>A 14555-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -18824,10 +18819,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45552</v>
+        <v>46100</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18840,7 +18835,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -18883,7 +18878,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 14557-2026</t>
+          <t>A 18687-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -18897,10 +18892,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46100</v>
+        <v>45763</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18913,7 +18908,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -18956,7 +18951,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 18449-2024</t>
+          <t>A 17895-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -18970,10 +18965,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45425</v>
+        <v>46122</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18986,7 +18981,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>0.9</v>
+        <v>6.6</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -19029,7 +19024,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 15567-2026</t>
+          <t>A 19706-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -19043,10 +19038,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46106</v>
+        <v>46134</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19059,7 +19054,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>5.7</v>
+        <v>0.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -19102,7 +19097,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 23662-2023</t>
+          <t>A 19685-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -19116,10 +19111,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45077</v>
+        <v>46134</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19131,13 +19126,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I237" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -19180,7 +19170,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 16200-2026</t>
+          <t>A 30200-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -19194,10 +19184,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>46111</v>
+        <v>46206</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19209,8 +19199,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -19253,7 +19248,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 58755-2022</t>
+          <t>A 33713-2026</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -19267,10 +19262,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>44903</v>
+        <v>46251</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19282,8 +19277,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I239" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -19326,7 +19326,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 14555-2026</t>
+          <t>A 30194-2026</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -19340,10 +19340,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46100</v>
+        <v>46206</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19355,8 +19355,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -19399,7 +19404,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 17895-2026</t>
+          <t>A 30198-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -19413,10 +19418,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>46122</v>
+        <v>46206</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19428,8 +19433,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I241" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -19472,7 +19482,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 22861-2024</t>
+          <t>A 33522-2026</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -19486,10 +19496,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45448</v>
+        <v>46248</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19503,11 +19513,11 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I242" t="n">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -19550,7 +19560,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>A 32463-2022</t>
+          <t>A 33524-2026</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -19564,10 +19574,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>44782</v>
+        <v>46248</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19581,11 +19591,11 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -19628,7 +19638,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 19706-2026</t>
+          <t>A 30539-2026</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -19638,14 +19648,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46134</v>
+        <v>46210</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19657,8 +19667,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I244" t="n">
-        <v>0.5</v>
+        <v>10.7</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -19701,7 +19716,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 19685-2026</t>
+          <t>A 39791-2024</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -19715,10 +19730,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46134</v>
+        <v>45553</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19731,7 +19746,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -19774,7 +19789,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>A 57670-2023</t>
+          <t>A 58013-2022</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -19788,10 +19803,10 @@
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45246</v>
+        <v>44900</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19804,7 +19819,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -19847,7 +19862,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>A 51626-2023</t>
+          <t>A 53791-2023</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -19861,10 +19876,10 @@
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45215</v>
+        <v>45231</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19876,8 +19891,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I247" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -19920,7 +19940,7 @@
     <row r="248" ht="15" customHeight="1">
       <c r="A248" t="inlineStr">
         <is>
-          <t>A 16265-2025</t>
+          <t>A 39660-2024</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -19934,10 +19954,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>45750</v>
+        <v>45552</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19950,7 +19970,7 @@
         </is>
       </c>
       <c r="I248" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -19993,7 +20013,7 @@
     <row r="249" ht="15" customHeight="1">
       <c r="A249" t="inlineStr">
         <is>
-          <t>A 4194-2024</t>
+          <t>A 18449-2024</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -20003,14 +20023,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D249" s="1" t="n">
-        <v>45324</v>
+        <v>45425</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20023,7 +20043,7 @@
         </is>
       </c>
       <c r="I249" t="n">
-        <v>28.9</v>
+        <v>0.9</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -20066,7 +20086,7 @@
     <row r="250" ht="15" customHeight="1">
       <c r="A250" t="inlineStr">
         <is>
-          <t>A 57225-2021</t>
+          <t>A 33523-2026</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -20080,10 +20100,10 @@
         </is>
       </c>
       <c r="D250" s="1" t="n">
-        <v>44483</v>
+        <v>46248</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20101,7 +20121,7 @@
         </is>
       </c>
       <c r="I250" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -20144,7 +20164,7 @@
     <row r="251" ht="15" customHeight="1">
       <c r="A251" t="inlineStr">
         <is>
-          <t>A 30200-2026</t>
+          <t>A 23662-2023</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -20158,10 +20178,10 @@
         </is>
       </c>
       <c r="D251" s="1" t="n">
-        <v>46206</v>
+        <v>45077</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20175,11 +20195,11 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I251" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -20222,7 +20242,7 @@
     <row r="252" ht="15" customHeight="1">
       <c r="A252" t="inlineStr">
         <is>
-          <t>A 33713-2026</t>
+          <t>A 33715-2026</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -20239,7 +20259,7 @@
         <v>46251</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20257,7 +20277,7 @@
         </is>
       </c>
       <c r="I252" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -20300,7 +20320,7 @@
     <row r="253" ht="15" customHeight="1">
       <c r="A253" t="inlineStr">
         <is>
-          <t>A 35448-2024</t>
+          <t>A 58755-2022</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -20314,10 +20334,10 @@
         </is>
       </c>
       <c r="D253" s="1" t="n">
-        <v>45531</v>
+        <v>44903</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20330,7 +20350,7 @@
         </is>
       </c>
       <c r="I253" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="J253" t="n">
         <v>0</v>
@@ -20373,7 +20393,7 @@
     <row r="254" ht="15" customHeight="1">
       <c r="A254" t="inlineStr">
         <is>
-          <t>A 35489-2024</t>
+          <t>A 22861-2024</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -20387,10 +20407,10 @@
         </is>
       </c>
       <c r="D254" s="1" t="n">
-        <v>45531</v>
+        <v>45448</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20402,8 +20422,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I254" t="n">
-        <v>0.7</v>
+        <v>3.9</v>
       </c>
       <c r="J254" t="n">
         <v>0</v>
@@ -20446,7 +20471,7 @@
     <row r="255" ht="15" customHeight="1">
       <c r="A255" t="inlineStr">
         <is>
-          <t>A 30194-2026</t>
+          <t>A 32463-2022</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -20460,10 +20485,10 @@
         </is>
       </c>
       <c r="D255" s="1" t="n">
-        <v>46206</v>
+        <v>44782</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20477,11 +20502,11 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I255" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -20524,7 +20549,7 @@
     <row r="256" ht="15" customHeight="1">
       <c r="A256" t="inlineStr">
         <is>
-          <t>A 41627-2022</t>
+          <t>A 36277-2026</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -20534,14 +20559,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D256" s="1" t="n">
-        <v>44827</v>
+        <v>46268</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20554,7 +20579,7 @@
         </is>
       </c>
       <c r="I256" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -20597,7 +20622,7 @@
     <row r="257" ht="15" customHeight="1">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A 41632-2022</t>
+          <t>A 36391-2026</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -20607,14 +20632,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D257" s="1" t="n">
-        <v>44827</v>
+        <v>46268</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20626,8 +20651,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I257" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J257" t="n">
         <v>0</v>
@@ -20670,7 +20700,7 @@
     <row r="258" ht="15" customHeight="1">
       <c r="A258" t="inlineStr">
         <is>
-          <t>A 30198-2026</t>
+          <t>A 36390-2026</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -20684,10 +20714,10 @@
         </is>
       </c>
       <c r="D258" s="1" t="n">
-        <v>46206</v>
+        <v>46268</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20705,7 +20735,7 @@
         </is>
       </c>
       <c r="I258" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="J258" t="n">
         <v>0</v>
@@ -20748,7 +20778,7 @@
     <row r="259" ht="15" customHeight="1">
       <c r="A259" t="inlineStr">
         <is>
-          <t>A 33522-2026</t>
+          <t>A 36387-2026</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -20762,10 +20792,10 @@
         </is>
       </c>
       <c r="D259" s="1" t="n">
-        <v>46248</v>
+        <v>46268</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20783,7 +20813,7 @@
         </is>
       </c>
       <c r="I259" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -20826,7 +20856,7 @@
     <row r="260" ht="15" customHeight="1">
       <c r="A260" t="inlineStr">
         <is>
-          <t>A 33524-2026</t>
+          <t>A 36384-2026</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -20840,10 +20870,10 @@
         </is>
       </c>
       <c r="D260" s="1" t="n">
-        <v>46248</v>
+        <v>46268</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20861,7 +20891,7 @@
         </is>
       </c>
       <c r="I260" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="J260" t="n">
         <v>0</v>
@@ -20904,7 +20934,7 @@
     <row r="261" ht="15" customHeight="1">
       <c r="A261" t="inlineStr">
         <is>
-          <t>A 48973-2023</t>
+          <t>A 36386-2026</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -20918,10 +20948,10 @@
         </is>
       </c>
       <c r="D261" s="1" t="n">
-        <v>45209</v>
+        <v>46268</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20933,8 +20963,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I261" t="n">
-        <v>4.5</v>
+        <v>1.2</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -20977,7 +21012,7 @@
     <row r="262" ht="15" customHeight="1">
       <c r="A262" t="inlineStr">
         <is>
-          <t>A 30539-2026</t>
+          <t>A 57670-2023</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -20991,10 +21026,10 @@
         </is>
       </c>
       <c r="D262" s="1" t="n">
-        <v>46210</v>
+        <v>45246</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21006,13 +21041,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I262" t="n">
-        <v>10.7</v>
+        <v>1.1</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -21055,7 +21085,7 @@
     <row r="263" ht="15" customHeight="1">
       <c r="A263" t="inlineStr">
         <is>
-          <t>A 62781-2023</t>
+          <t>A 51626-2023</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -21069,10 +21099,10 @@
         </is>
       </c>
       <c r="D263" s="1" t="n">
-        <v>45268</v>
+        <v>45215</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21085,7 +21115,7 @@
         </is>
       </c>
       <c r="I263" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -21128,7 +21158,7 @@
     <row r="264" ht="15" customHeight="1">
       <c r="A264" t="inlineStr">
         <is>
-          <t>A 4666-2024</t>
+          <t>A 4194-2024</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -21138,14 +21168,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D264" s="1" t="n">
-        <v>45328</v>
+        <v>45324</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21158,7 +21188,7 @@
         </is>
       </c>
       <c r="I264" t="n">
-        <v>0.5</v>
+        <v>28.9</v>
       </c>
       <c r="J264" t="n">
         <v>0</v>
@@ -21201,7 +21231,7 @@
     <row r="265" ht="15" customHeight="1">
       <c r="A265" t="inlineStr">
         <is>
-          <t>A 59438-2022</t>
+          <t>A 37453-2026</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -21215,10 +21245,10 @@
         </is>
       </c>
       <c r="D265" s="1" t="n">
-        <v>44907</v>
+        <v>46275</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21231,7 +21261,7 @@
         </is>
       </c>
       <c r="I265" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J265" t="n">
         <v>0</v>
@@ -21274,7 +21304,7 @@
     <row r="266" ht="15" customHeight="1">
       <c r="A266" t="inlineStr">
         <is>
-          <t>A 57974-2022</t>
+          <t>A 57225-2021</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -21288,10 +21318,10 @@
         </is>
       </c>
       <c r="D266" s="1" t="n">
-        <v>44900</v>
+        <v>44483</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21303,8 +21333,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I266" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J266" t="n">
         <v>0</v>
@@ -21347,7 +21382,7 @@
     <row r="267" ht="15" customHeight="1">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A 33523-2026</t>
+          <t>A 31901-2026</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -21361,10 +21396,10 @@
         </is>
       </c>
       <c r="D267" s="1" t="n">
-        <v>46248</v>
+        <v>46231</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21376,13 +21411,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I267" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -21425,7 +21455,7 @@
     <row r="268" ht="15" customHeight="1">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A 4218-2023</t>
+          <t>A 35448-2024</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -21439,10 +21469,10 @@
         </is>
       </c>
       <c r="D268" s="1" t="n">
-        <v>44951</v>
+        <v>45531</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21455,7 +21485,7 @@
         </is>
       </c>
       <c r="I268" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J268" t="n">
         <v>0</v>
@@ -21498,7 +21528,7 @@
     <row r="269" ht="15" customHeight="1">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A 17497-2025</t>
+          <t>A 35489-2024</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -21512,10 +21542,10 @@
         </is>
       </c>
       <c r="D269" s="1" t="n">
-        <v>45757</v>
+        <v>45531</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21528,7 +21558,7 @@
         </is>
       </c>
       <c r="I269" t="n">
-        <v>49.4</v>
+        <v>0.7</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -21571,7 +21601,7 @@
     <row r="270" ht="15" customHeight="1">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A 33715-2026</t>
+          <t>A 41627-2022</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -21581,14 +21611,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D270" s="1" t="n">
-        <v>46251</v>
+        <v>44827</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21600,13 +21630,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I270" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -21649,7 +21674,7 @@
     <row r="271" ht="15" customHeight="1">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A 51889-2024</t>
+          <t>A 41632-2022</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -21659,14 +21684,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D271" s="1" t="n">
-        <v>45607</v>
+        <v>44827</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21679,7 +21704,7 @@
         </is>
       </c>
       <c r="I271" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J271" t="n">
         <v>0</v>
@@ -21722,7 +21747,7 @@
     <row r="272" ht="15" customHeight="1">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A 34862-2023</t>
+          <t>A 36393-2026</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -21736,10 +21761,10 @@
         </is>
       </c>
       <c r="D272" s="1" t="n">
-        <v>45142</v>
+        <v>46268</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21751,8 +21776,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I272" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -21795,7 +21825,7 @@
     <row r="273" ht="15" customHeight="1">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A 1550-2023</t>
+          <t>A 48973-2023</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -21809,10 +21839,10 @@
         </is>
       </c>
       <c r="D273" s="1" t="n">
-        <v>44937</v>
+        <v>45209</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21824,13 +21854,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I273" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -21873,7 +21898,7 @@
     <row r="274" ht="15" customHeight="1">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A 19874-2022</t>
+          <t>A 62781-2023</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -21887,10 +21912,10 @@
         </is>
       </c>
       <c r="D274" s="1" t="n">
-        <v>44697</v>
+        <v>45268</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21903,7 +21928,7 @@
         </is>
       </c>
       <c r="I274" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -21946,7 +21971,7 @@
     <row r="275" ht="15" customHeight="1">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A 36277-2026</t>
+          <t>A 4666-2024</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -21960,10 +21985,10 @@
         </is>
       </c>
       <c r="D275" s="1" t="n">
-        <v>46268</v>
+        <v>45328</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21976,7 +22001,7 @@
         </is>
       </c>
       <c r="I275" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J275" t="n">
         <v>0</v>
@@ -22019,7 +22044,7 @@
     <row r="276" ht="15" customHeight="1">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A 36391-2026</t>
+          <t>A 59438-2022</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -22033,10 +22058,10 @@
         </is>
       </c>
       <c r="D276" s="1" t="n">
-        <v>46268</v>
+        <v>44907</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22048,13 +22073,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I276" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -22097,7 +22117,7 @@
     <row r="277" ht="15" customHeight="1">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A 28196-2022</t>
+          <t>A 38482-2026</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -22107,14 +22127,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D277" s="1" t="n">
-        <v>44746</v>
+        <v>46282</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22127,7 +22147,7 @@
         </is>
       </c>
       <c r="I277" t="n">
-        <v>3.7</v>
+        <v>6.2</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -22170,7 +22190,7 @@
     <row r="278" ht="15" customHeight="1">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A 36390-2026</t>
+          <t>A 57974-2022</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -22184,10 +22204,10 @@
         </is>
       </c>
       <c r="D278" s="1" t="n">
-        <v>46268</v>
+        <v>44900</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22199,13 +22219,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I278" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="J278" t="n">
         <v>0</v>
@@ -22248,7 +22263,7 @@
     <row r="279" ht="15" customHeight="1">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A 36387-2026</t>
+          <t>A 38483-2026</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -22262,10 +22277,10 @@
         </is>
       </c>
       <c r="D279" s="1" t="n">
-        <v>46268</v>
+        <v>46282</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22277,13 +22292,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I279" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -22326,7 +22336,7 @@
     <row r="280" ht="15" customHeight="1">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A 36384-2026</t>
+          <t>A 4218-2023</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -22340,10 +22350,10 @@
         </is>
       </c>
       <c r="D280" s="1" t="n">
-        <v>46268</v>
+        <v>44951</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22355,13 +22365,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I280" t="n">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="J280" t="n">
         <v>0</v>
@@ -22404,7 +22409,7 @@
     <row r="281" ht="15" customHeight="1">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A 36386-2026</t>
+          <t>A 17497-2025</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -22418,10 +22423,10 @@
         </is>
       </c>
       <c r="D281" s="1" t="n">
-        <v>46268</v>
+        <v>45757</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22433,13 +22438,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H281" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I281" t="n">
-        <v>1.2</v>
+        <v>49.4</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -22482,7 +22482,7 @@
     <row r="282" ht="15" customHeight="1">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A 20976-2025</t>
+          <t>A 51889-2024</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -22496,10 +22496,10 @@
         </is>
       </c>
       <c r="D282" s="1" t="n">
-        <v>45777</v>
+        <v>45607</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22511,13 +22511,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I282" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -22560,7 +22555,7 @@
     <row r="283" ht="15" customHeight="1">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A 46088-2024</t>
+          <t>A 34862-2023</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -22574,10 +22569,10 @@
         </is>
       </c>
       <c r="D283" s="1" t="n">
-        <v>45581</v>
+        <v>45142</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22589,13 +22584,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I283" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J283" t="n">
         <v>0</v>
@@ -22638,7 +22628,7 @@
     <row r="284" ht="15" customHeight="1">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A 37453-2026</t>
+          <t>A 1550-2023</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -22652,10 +22642,10 @@
         </is>
       </c>
       <c r="D284" s="1" t="n">
-        <v>46275</v>
+        <v>44937</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22667,8 +22657,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I284" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J284" t="n">
         <v>0</v>
@@ -22711,7 +22706,7 @@
     <row r="285" ht="15" customHeight="1">
       <c r="A285" t="inlineStr">
         <is>
-          <t>A 31901-2026</t>
+          <t>A 19874-2022</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -22725,10 +22720,10 @@
         </is>
       </c>
       <c r="D285" s="1" t="n">
-        <v>46231</v>
+        <v>44697</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22741,7 +22736,7 @@
         </is>
       </c>
       <c r="I285" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="J285" t="n">
         <v>0</v>
@@ -22784,7 +22779,7 @@
     <row r="286" ht="15" customHeight="1">
       <c r="A286" t="inlineStr">
         <is>
-          <t>A 11730-2025</t>
+          <t>A 28196-2022</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -22794,14 +22789,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D286" s="1" t="n">
-        <v>45727</v>
+        <v>44746</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22814,7 +22809,7 @@
         </is>
       </c>
       <c r="I286" t="n">
-        <v>11.2</v>
+        <v>3.7</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -22857,7 +22852,7 @@
     <row r="287" ht="15" customHeight="1">
       <c r="A287" t="inlineStr">
         <is>
-          <t>A 36393-2026</t>
+          <t>A 20976-2025</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -22871,10 +22866,10 @@
         </is>
       </c>
       <c r="D287" s="1" t="n">
-        <v>46268</v>
+        <v>45777</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22892,7 +22887,7 @@
         </is>
       </c>
       <c r="I287" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="J287" t="n">
         <v>0</v>
@@ -22935,7 +22930,7 @@
     <row r="288" ht="15" customHeight="1">
       <c r="A288" t="inlineStr">
         <is>
-          <t>A 9109-2025</t>
+          <t>A 46088-2024</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -22949,10 +22944,10 @@
         </is>
       </c>
       <c r="D288" s="1" t="n">
-        <v>45713</v>
+        <v>45581</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22964,8 +22959,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I288" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -23008,7 +23008,7 @@
     <row r="289" ht="15" customHeight="1">
       <c r="A289" t="inlineStr">
         <is>
-          <t>A 12328-2025</t>
+          <t>A 11730-2025</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -23018,14 +23018,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D289" s="1" t="n">
-        <v>45730</v>
+        <v>45727</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23038,7 +23038,7 @@
         </is>
       </c>
       <c r="I289" t="n">
-        <v>2.9</v>
+        <v>11.2</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -23081,7 +23081,7 @@
     <row r="290" ht="15" customHeight="1">
       <c r="A290" t="inlineStr">
         <is>
-          <t>A 30593-2024</t>
+          <t>A 9109-2025</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -23095,10 +23095,10 @@
         </is>
       </c>
       <c r="D290" s="1" t="n">
-        <v>45493</v>
+        <v>45713</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         </is>
       </c>
       <c r="I290" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J290" t="n">
         <v>0</v>
@@ -23154,7 +23154,7 @@
     <row r="291" ht="15" customHeight="1">
       <c r="A291" t="inlineStr">
         <is>
-          <t>A 14505-2024</t>
+          <t>A 12328-2025</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -23168,10 +23168,10 @@
         </is>
       </c>
       <c r="D291" s="1" t="n">
-        <v>45394</v>
+        <v>45730</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         </is>
       </c>
       <c r="I291" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J291" t="n">
         <v>0</v>
@@ -23227,7 +23227,7 @@
     <row r="292" ht="15" customHeight="1">
       <c r="A292" t="inlineStr">
         <is>
-          <t>A 21014-2024</t>
+          <t>A 30593-2024</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -23241,10 +23241,10 @@
         </is>
       </c>
       <c r="D292" s="1" t="n">
-        <v>45439</v>
+        <v>45493</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23257,7 +23257,7 @@
         </is>
       </c>
       <c r="I292" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -23300,7 +23300,7 @@
     <row r="293" ht="15" customHeight="1">
       <c r="A293" t="inlineStr">
         <is>
-          <t>A 48969-2023</t>
+          <t>A 14505-2024</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -23314,10 +23314,10 @@
         </is>
       </c>
       <c r="D293" s="1" t="n">
-        <v>45209</v>
+        <v>45394</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         </is>
       </c>
       <c r="I293" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J293" t="n">
         <v>0</v>
@@ -23373,7 +23373,7 @@
     <row r="294" ht="15" customHeight="1">
       <c r="A294" t="inlineStr">
         <is>
-          <t>A 58006-2024</t>
+          <t>A 21014-2024</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -23387,10 +23387,10 @@
         </is>
       </c>
       <c r="D294" s="1" t="n">
-        <v>45631</v>
+        <v>45439</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         </is>
       </c>
       <c r="I294" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -23446,7 +23446,7 @@
     <row r="295" ht="15" customHeight="1">
       <c r="A295" t="inlineStr">
         <is>
-          <t>A 43559-2024</t>
+          <t>A 48969-2023</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -23460,10 +23460,10 @@
         </is>
       </c>
       <c r="D295" s="1" t="n">
-        <v>45569</v>
+        <v>45209</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         </is>
       </c>
       <c r="I295" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J295" t="n">
         <v>0</v>
@@ -23519,7 +23519,7 @@
     <row r="296" ht="15" customHeight="1">
       <c r="A296" t="inlineStr">
         <is>
-          <t>A 18690-2025</t>
+          <t>A 58006-2024</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -23533,10 +23533,10 @@
         </is>
       </c>
       <c r="D296" s="1" t="n">
-        <v>45763</v>
+        <v>45631</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23548,13 +23548,8 @@
           <t>TÖREBODA</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I296" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J296" t="n">
         <v>0</v>
@@ -23597,7 +23592,7 @@
     <row r="297" ht="15" customHeight="1">
       <c r="A297" t="inlineStr">
         <is>
-          <t>A 38482-2026</t>
+          <t>A 43559-2024</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -23611,10 +23606,10 @@
         </is>
       </c>
       <c r="D297" s="1" t="n">
-        <v>46282</v>
+        <v>45569</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23627,7 +23622,7 @@
         </is>
       </c>
       <c r="I297" t="n">
-        <v>6.2</v>
+        <v>1</v>
       </c>
       <c r="J297" t="n">
         <v>0</v>
@@ -23670,7 +23665,7 @@
     <row r="298" ht="15" customHeight="1">
       <c r="A298" t="inlineStr">
         <is>
-          <t>A 48734-2024</t>
+          <t>A 18690-2025</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -23684,10 +23679,10 @@
         </is>
       </c>
       <c r="D298" s="1" t="n">
-        <v>45593</v>
+        <v>45763</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23699,8 +23694,13 @@
           <t>TÖREBODA</t>
         </is>
       </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I298" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J298" t="n">
         <v>0</v>
@@ -23743,7 +23743,7 @@
     <row r="299" ht="15" customHeight="1">
       <c r="A299" t="inlineStr">
         <is>
-          <t>A 38483-2026</t>
+          <t>A 48734-2024</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -23757,10 +23757,10 @@
         </is>
       </c>
       <c r="D299" s="1" t="n">
-        <v>46282</v>
+        <v>45593</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         </is>
       </c>
       <c r="I299" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J299" t="n">
         <v>0</v>
@@ -23833,7 +23833,7 @@
         <v>45811</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>45811</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23979,7 +23979,7 @@
         <v>45569</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24052,7 +24052,7 @@
         <v>45763</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>45831</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24198,7 +24198,7 @@
         <v>45835</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24271,7 +24271,7 @@
         <v>45835</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45841</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>45841</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>45841</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24578,7 +24578,7 @@
         <v>45841</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45841</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45841</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>45841</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45764</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>45720</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>45741</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25092,24 +25092,24 @@
     <row r="317" ht="15" customHeight="1">
       <c r="A317" t="inlineStr">
         <is>
-          <t>A 10448-2025</t>
+          <t>S 277-2025</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D317" s="1" t="n">
-        <v>45720</v>
+        <v>45685</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25122,7 +25122,7 @@
         </is>
       </c>
       <c r="I317" t="n">
-        <v>1.5</v>
+        <v>186</v>
       </c>
       <c r="J317" t="n">
         <v>0</v>
@@ -25165,7 +25165,7 @@
     <row r="318" ht="15" customHeight="1">
       <c r="A318" t="inlineStr">
         <is>
-          <t>S 277-2025</t>
+          <t>S 671-2025</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -25179,10 +25179,10 @@
         </is>
       </c>
       <c r="D318" s="1" t="n">
-        <v>45685</v>
+        <v>45716</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25195,7 +25195,7 @@
         </is>
       </c>
       <c r="I318" t="n">
-        <v>186</v>
+        <v>56.1</v>
       </c>
       <c r="J318" t="n">
         <v>0</v>
@@ -25238,7 +25238,7 @@
     <row r="319" ht="15" customHeight="1">
       <c r="A319" t="inlineStr">
         <is>
-          <t>S 671-2025</t>
+          <t>S 670-2025</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -25255,7 +25255,7 @@
         <v>45716</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         </is>
       </c>
       <c r="I319" t="n">
-        <v>56.1</v>
+        <v>23.4</v>
       </c>
       <c r="J319" t="n">
         <v>0</v>
@@ -25308,10 +25308,10 @@
       </c>
       <c r="V319" s="2" t="inlineStr"/>
     </row>
-    <row r="320" ht="15" customHeight="1">
+    <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>S 670-2025</t>
+          <t>S 178-2026</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -25321,14 +25321,14 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D320" s="1" t="n">
-        <v>45716</v>
+        <v>46045</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         </is>
       </c>
       <c r="I320" t="n">
-        <v>23.4</v>
+        <v>12.5</v>
       </c>
       <c r="J320" t="n">
         <v>0</v>
@@ -25380,79 +25380,6 @@
         <v>0</v>
       </c>
       <c r="V320" s="2" t="inlineStr"/>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>S 178-2026</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D321" s="1" t="n">
-        <v>46045</v>
-      </c>
-      <c r="E321" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>VÄSTRA GÖTALANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>TÖREBODA</t>
-        </is>
-      </c>
-      <c r="I321" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J321" t="n">
-        <v>0</v>
-      </c>
-      <c r="K321" t="n">
-        <v>0</v>
-      </c>
-      <c r="L321" t="n">
-        <v>0</v>
-      </c>
-      <c r="M321" t="n">
-        <v>0</v>
-      </c>
-      <c r="N321" t="n">
-        <v>0</v>
-      </c>
-      <c r="O321" t="n">
-        <v>0</v>
-      </c>
-      <c r="P321" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
-      <c r="R321" t="n">
-        <v>0</v>
-      </c>
-      <c r="S321" t="n">
-        <v>0</v>
-      </c>
-      <c r="T321" t="n">
-        <v>0</v>
-      </c>
-      <c r="U321" t="n">
-        <v>0</v>
-      </c>
-      <c r="V321" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt TÖREBODA.xlsx
+++ b/Översikt TÖREBODA.xlsx
@@ -601,7 +601,7 @@
         <v>45587</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44747</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45191</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>46288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44986</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>46150</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46085</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45552</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>45264</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>44608</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>46206</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45552</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>44964</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44610</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>45938</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>45757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44608</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45742</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>44937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45632</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>45621</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>46212</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>45166</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>46274</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>45729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44690</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44986</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44508</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44733</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>44740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>44818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44726</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44719</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44507</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44754</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44532</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>44601</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>44719</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>44847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>44847</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>44614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>44614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44531</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44852</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44818</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>45369</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>45209</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>44860</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>45373</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45460</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>45373</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45443</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>44986</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45457</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44868</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>44903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45531</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45631</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45282</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44853</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45439</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45394</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45763</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45209</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>45493</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45569</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>45341</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45642</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>45885</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>45885</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>45888</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>45481</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>45885</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45414</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45627</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>44907</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>44900</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>44571</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>44988</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>44900</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>45912</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>45684</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>44924</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>46057</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>45803</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>45915</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>46062</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45919</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45127</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45924</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44958</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45531</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45099</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>46078</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>45929</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>45399</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>45051</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>44698</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>46085</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>45938</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>45938</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>45937</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45937</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>44923</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>45579</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>46100</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>45553</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>46106</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>46111</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>45811</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>45954</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>45954</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>45811</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>46100</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45328</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45961</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>46122</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44853</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>45971</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45972</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>45974</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45077</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>45972</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45972</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44483</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>45002</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>44987</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>46134</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45627</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>46134</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>45664</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>45664</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45750</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>45699</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>44782</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>44756</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>46140</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>46009</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45643</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45569</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45763</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44473</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>45049</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>45831</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>45425</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>45757</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44924</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>45754</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>46146</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>45096</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45553</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>46152</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>46152</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>46152</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>46152</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44890</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>46152</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>46152</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>46152</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>46152</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>45665</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45835</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45215</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>45231</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45835</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>45450</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>45841</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>45384</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45841</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>45841</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45841</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45841</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45841</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45841</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45191</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45764</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>46168</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>46168</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45720</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45741</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45637</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45142</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45309</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45145</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45133</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>44937</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>45706</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45460</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45166</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45556</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45096</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>45443</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45457</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45552</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45627</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45555</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45720</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45268</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>44664</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45145</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45328</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45077</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>46206</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>46206</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>46206</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>46251</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>45607</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>46210</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45236</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44697</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45156</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>45531</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>45237</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45763</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>44900</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>46251</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>44749</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>44746</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>46268</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>46268</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>46268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>46268</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45530</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>46268</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>46268</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44950</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45448</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>46231</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45694</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>46275</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45233</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45405</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44978</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>46268</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44740</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45651</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45485</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>44858</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>46282</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>44901</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>46282</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45685</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>46288</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>45268</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>44951</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>44923</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45344</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>46248</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>46248</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>44964</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>44816</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>46288</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>46288</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>44599</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>46248</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44900</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45460</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45246</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>44901</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45076</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>44937</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>44972</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44746</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45142</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45699</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>45562</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45349</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>44987</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>44987</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>44956</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>44792</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45625</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>45324</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45322</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45056</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>44741</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44894</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45750</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45553</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44978</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>44827</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44827</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45552</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45700</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45552</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>45273</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>45350</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>45245</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45531</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>44907</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45352</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45244</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45082</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45777</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45581</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45727</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45713</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45730</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45685</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45716</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45716</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>46045</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>

--- a/Översikt TÖREBODA.xlsx
+++ b/Översikt TÖREBODA.xlsx
@@ -601,7 +601,7 @@
         <v>45587</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44747</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45191</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>46288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44986</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>46150</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46085</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45552</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>45264</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>44608</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>46206</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>45552</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>44964</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>44610</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2835,7 +2835,7 @@
         <v>45938</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>45757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>44608</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45742</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>44937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45632</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>44985</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>45621</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
         <v>46212</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>45166</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>46274</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>45729</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44690</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44986</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44508</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44733</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>44740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>44818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44726</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44719</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44507</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44754</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44532</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>44601</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>44719</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>44847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>44847</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>44614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>44614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44531</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44852</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44818</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>45369</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>45209</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>44860</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>45373</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45460</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>45373</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45443</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>44986</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7072,7 +7072,7 @@
         <v>45457</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44868</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>44903</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45531</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45631</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         <v>45593</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>45282</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44853</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45439</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>45394</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         <v>45763</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45209</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>45493</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45569</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>45341</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45642</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>45885</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>45885</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         <v>45888</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8474,7 +8474,7 @@
         <v>45481</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>45885</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8620,7 +8620,7 @@
         <v>45414</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>45627</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>44907</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>44900</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>44571</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>44988</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>44900</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>45912</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         <v>45684</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>44924</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>46057</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>45803</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9496,7 +9496,7 @@
         <v>45915</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>46062</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45919</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>45127</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45924</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>44958</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45531</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10007,7 +10007,7 @@
         <v>45099</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10080,7 +10080,7 @@
         <v>46078</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>45929</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10226,7 +10226,7 @@
         <v>45399</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>45051</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10377,7 +10377,7 @@
         <v>44698</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>46085</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>45938</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10596,7 +10596,7 @@
         <v>45938</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>45937</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45937</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>44923</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>45579</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>46100</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>45553</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>46106</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>46111</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>45811</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>45954</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>45954</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>45811</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>46100</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45328</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45961</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>46122</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44853</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>45971</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>45972</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>45974</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>45077</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>45972</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45972</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>44483</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>45002</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>44987</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>46134</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>45627</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>46134</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>45664</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>45664</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>45750</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>45699</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>44782</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>44756</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>46140</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>46009</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45643</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>45569</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>45763</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44473</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>45049</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>45831</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13853,7 +13853,7 @@
         <v>45425</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>45757</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>44924</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>45754</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>46146</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>45096</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>45553</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>46152</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
         <v>46152</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14515,7 +14515,7 @@
         <v>46152</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14588,7 +14588,7 @@
         <v>46152</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44890</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>46152</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>46152</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>46152</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>46152</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>45665</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45835</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45215</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>45231</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45835</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>45450</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>45841</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>45384</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45841</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>45841</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>45841</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45841</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>45841</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>45841</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45191</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45764</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>46168</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>46168</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>45720</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45741</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
         <v>45637</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45142</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16692,7 +16692,7 @@
         <v>45309</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>45145</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16838,7 +16838,7 @@
         <v>45133</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>44937</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16989,7 +16989,7 @@
         <v>45706</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17062,7 +17062,7 @@
         <v>45460</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>45166</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45556</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45096</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>45443</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45457</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45552</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17583,7 +17583,7 @@
         <v>45627</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45555</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17729,7 +17729,7 @@
         <v>45720</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17802,7 +17802,7 @@
         <v>45268</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17875,7 +17875,7 @@
         <v>44664</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45145</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18021,7 +18021,7 @@
         <v>45328</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18094,7 +18094,7 @@
         <v>45077</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18172,7 +18172,7 @@
         <v>46206</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>46206</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18328,7 +18328,7 @@
         <v>46206</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>46251</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>45607</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>46210</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18635,7 +18635,7 @@
         <v>45236</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18708,7 +18708,7 @@
         <v>44697</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18781,7 +18781,7 @@
         <v>45156</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>45531</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>45237</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>45763</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>44900</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>46251</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>44749</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>44746</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>46268</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>46268</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>46268</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>46268</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45530</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>46268</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>46268</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>44950</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45448</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>46231</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45694</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>46275</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45233</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45405</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>44978</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20500,7 +20500,7 @@
         <v>46268</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>44740</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45651</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>45485</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>44858</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>46282</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>44901</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>46282</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45685</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>46288</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>45268</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>44951</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>44923</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45344</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>46248</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>46248</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>44964</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>44816</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>46288</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>46288</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21990,7 +21990,7 @@
         <v>44599</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>46248</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22141,7 +22141,7 @@
         <v>44900</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22214,7 +22214,7 @@
         <v>45460</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45246</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>44901</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45076</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>44937</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22584,7 +22584,7 @@
         <v>44972</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>44746</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45142</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22803,7 +22803,7 @@
         <v>45699</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>45562</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45349</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>44987</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>44987</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>44956</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>44792</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45625</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>45324</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45322</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45056</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>44741</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>44894</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45750</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45553</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>44978</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>44827</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44827</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45552</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24190,7 +24190,7 @@
         <v>45700</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24263,7 +24263,7 @@
         <v>45552</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24336,7 +24336,7 @@
         <v>45273</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24409,7 +24409,7 @@
         <v>45350</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24482,7 +24482,7 @@
         <v>45245</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45531</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>44907</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>45352</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45244</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45082</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>45777</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45581</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45727</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25149,7 +25149,7 @@
         <v>45713</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>45730</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45685</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45716</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45716</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>46045</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>

--- a/Översikt TÖREBODA.xlsx
+++ b/Översikt TÖREBODA.xlsx
@@ -601,7 +601,7 @@
         <v>45587</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44747</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45191</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>46288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44986</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45722</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46150</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44900</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46085</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45552</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45727</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45264</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45552</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>46206</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>44608</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>45166</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>45729</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>45632</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>45938</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45621</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>45757</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>45742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>44964</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>44985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44610</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46212</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>46274</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44986</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44508</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44733</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>44740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>44726</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44616</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44818</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44614</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44719</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44507</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44754</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44532</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>44601</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>44719</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>44847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>44847</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>44614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>44614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44531</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44852</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44818</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44853</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45443</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>45237</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45076</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>45457</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>44698</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45145</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45245</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44956</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45552</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45373</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45051</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>44599</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>45077</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>45713</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45627</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>45643</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44664</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>45885</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45384</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>45344</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45651</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44816</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45730</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45166</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>44741</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>46009</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45309</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45888</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45531</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45664</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>44571</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45450</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45485</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>45493</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45394</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45439</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45209</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45684</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>45569</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>45763</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45915</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45912</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45593</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45803</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45919</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>45811</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45924</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>46057</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45929</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45460</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>45460</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>45282</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>46062</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>44987</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>44987</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>44901</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>45937</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45938</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45938</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45937</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>46078</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45811</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45369</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>45099</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>45954</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>46085</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>45954</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45961</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>44749</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45971</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45457</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45972</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>45096</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>45972</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45972</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>46100</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44890</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44950</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>44740</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45974</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45625</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44894</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>46106</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45627</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>46111</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45569</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45341</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45481</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45763</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45350</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>46100</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44978</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>46122</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44924</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>45233</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44756</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44860</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45831</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>46134</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45142</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>46134</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45579</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45835</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>45835</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45399</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45552</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44901</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44924</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45841</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45236</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45841</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45841</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45841</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>45841</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45750</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45841</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45841</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45764</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>44900</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44964</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45720</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45530</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45741</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45328</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44978</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45244</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45443</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>44853</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45145</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45553</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45082</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45405</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>46140</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44473</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45352</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45268</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45706</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45553</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>46146</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45349</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45555</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45664</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>46152</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>46152</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>46152</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>46152</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>46152</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>46152</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>46152</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45460</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>45754</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>46152</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45665</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45685</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>45273</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>45531</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45720</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45096</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45637</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44972</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45191</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45627</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>46168</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44792</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46168</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45156</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45322</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>45373</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45642</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44937</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44900</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45885</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45885</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44868</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45049</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45750</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45694</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45133</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45056</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44987</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44986</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45699</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45002</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>44958</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44923</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>44923</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45556</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>44746</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>46206</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>46206</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>46206</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45414</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>46210</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>44907</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45562</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45700</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>45127</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45763</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>46268</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>46268</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>46268</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21701,7 +21701,7 @@
         <v>46268</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>46268</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>46268</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>46275</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>46231</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>46268</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45553</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>44900</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45231</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>46282</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>46282</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45552</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45425</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>45077</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44903</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>46288</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46288</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46288</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45448</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>46248</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>46248</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44782</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>46248</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45246</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>46251</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45215</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45324</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44483</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>46251</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>46296</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>45531</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45531</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44827</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>44827</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45209</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45268</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45328</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44907</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44900</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44951</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45757</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45607</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45142</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44937</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44697</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44746</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>45777</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45581</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45727</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45685</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45716</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45716</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>46045</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>

--- a/Översikt TÖREBODA.xlsx
+++ b/Översikt TÖREBODA.xlsx
@@ -601,7 +601,7 @@
         <v>45587</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44747</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45191</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>46288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44986</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45722</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46150</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44900</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46085</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45552</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45727</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45264</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45552</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>46206</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>44608</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>45166</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>45729</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>45632</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>45938</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>45621</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>45757</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>44937</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>45742</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>44964</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>44985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>44610</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46212</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>46274</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44986</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44508</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44733</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>44740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>44726</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>44616</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44818</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44614</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>44719</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44507</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44754</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44532</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>44601</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>44719</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>44847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>44847</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>44614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>44614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44531</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44852</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44818</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44853</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45443</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>45237</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45076</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>45457</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>44698</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45145</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45245</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44956</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45552</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45373</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>45051</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45699</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>44599</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>45077</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>45713</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45627</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>45643</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44664</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>45885</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45384</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>45344</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45651</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44816</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45730</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45166</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>44741</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>46009</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45309</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>45888</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45531</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>45664</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         <v>44571</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         <v>45450</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45485</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>45493</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45394</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45439</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>45209</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45684</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>45569</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>45763</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45915</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45912</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45593</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45803</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45919</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>45811</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45924</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>46057</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45929</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45460</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>45460</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>45282</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>46062</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>44988</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>44987</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>44987</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10898,7 +10898,7 @@
         <v>44901</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>45937</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45938</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45938</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>45937</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>46078</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45811</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45369</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11492,7 +11492,7 @@
         <v>45099</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>45954</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11638,7 +11638,7 @@
         <v>46085</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>45954</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>45961</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>44749</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45971</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45457</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45972</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>45096</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>45972</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45972</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>46100</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>44890</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44950</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>44740</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45974</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>45625</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12831,7 +12831,7 @@
         <v>44894</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>46106</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12977,7 +12977,7 @@
         <v>45627</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>46111</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45569</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45341</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45481</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>45763</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>45350</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>46100</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44978</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>46122</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44924</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>45233</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44756</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44860</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45831</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>46134</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45142</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14233,7 +14233,7 @@
         <v>46134</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>45579</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>45835</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>45835</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>45399</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>45552</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44901</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44924</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45841</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45236</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45841</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>45841</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45841</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15202,7 +15202,7 @@
         <v>45841</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>45750</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15353,7 +15353,7 @@
         <v>45841</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15431,7 +15431,7 @@
         <v>45841</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45764</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15582,7 +15582,7 @@
         <v>44900</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>44964</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15728,7 +15728,7 @@
         <v>45720</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45530</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15874,7 +15874,7 @@
         <v>45741</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>45328</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16020,7 +16020,7 @@
         <v>44978</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16093,7 +16093,7 @@
         <v>45244</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16166,7 +16166,7 @@
         <v>45443</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>44853</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>45145</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>45553</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>45082</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16536,7 +16536,7 @@
         <v>45405</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>46140</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>44473</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16760,7 +16760,7 @@
         <v>45352</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45268</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45706</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45553</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>46146</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45349</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45555</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45664</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>46152</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>46152</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>46152</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>46152</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>46152</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>46152</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>46152</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         <v>45460</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>45754</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18001,7 +18001,7 @@
         <v>46152</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18074,7 +18074,7 @@
         <v>45665</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45685</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>45273</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18293,7 +18293,7 @@
         <v>45531</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45720</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18439,7 +18439,7 @@
         <v>45096</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18517,7 +18517,7 @@
         <v>45637</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18590,7 +18590,7 @@
         <v>44972</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18663,7 +18663,7 @@
         <v>45191</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18736,7 +18736,7 @@
         <v>45627</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18809,7 +18809,7 @@
         <v>46168</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44792</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>46168</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45156</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
         <v>45322</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19184,7 +19184,7 @@
         <v>45373</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19257,7 +19257,7 @@
         <v>45642</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44937</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>44900</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45885</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45885</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>44868</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45049</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45750</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45694</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45133</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45056</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44987</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>44986</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45699</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45002</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>44958</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>44923</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>44923</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45556</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>44746</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>46206</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>46206</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>46206</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>45414</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>46210</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21107,7 +21107,7 @@
         <v>44907</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         <v>45562</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45700</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>45127</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21399,7 +21399,7 @@
         <v>45763</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21472,7 +21472,7 @@
         <v>46268</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>46268</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>46268</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21701,7 +21701,7 @@
         <v>46268</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>46268</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>46268</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21935,7 +21935,7 @@
         <v>46275</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>46231</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>46268</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22159,7 +22159,7 @@
         <v>45553</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>44900</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22305,7 +22305,7 @@
         <v>45231</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>46282</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>46282</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45552</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22602,7 +22602,7 @@
         <v>45425</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>45077</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>44903</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>46288</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>46288</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46288</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45448</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>46248</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>46248</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23284,7 +23284,7 @@
         <v>44782</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>46248</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45246</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>46251</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45215</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45324</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>44483</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>46251</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23893,7 +23893,7 @@
         <v>46296</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>45531</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>45531</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24112,7 +24112,7 @@
         <v>44827</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>44827</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24258,7 +24258,7 @@
         <v>45209</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>45268</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45328</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>44907</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>44900</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>44951</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>45757</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>45607</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45142</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24915,7 +24915,7 @@
         <v>44937</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44697</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>44746</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25139,7 +25139,7 @@
         <v>45777</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45581</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45727</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45685</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45716</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45716</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>46045</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>

--- a/Översikt TÖREBODA.xlsx
+++ b/Översikt TÖREBODA.xlsx
@@ -601,7 +601,7 @@
         <v>45587</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44747</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45191</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>46288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44986</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>46150</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46085</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45552</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45552</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>44608</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45264</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45727</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>46206</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>44985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44964</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44610</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>44937</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45729</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45632</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45938</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>45621</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>45757</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>45166</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>45742</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46212</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>46274</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44690</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44986</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44508</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44733</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>44740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>44818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44726</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44719</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44847</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44847</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44507</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44614</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>44719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>44614</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>44532</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>44579</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>44601</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>44531</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>44754</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44719</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>45056</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>45209</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>45096</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44852</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>44741</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44818</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45553</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>44894</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>44890</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45215</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44860</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>45231</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>45460</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45450</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>45750</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45373</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>45443</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>45384</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45553</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>45369</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44978</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>44986</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45457</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>44827</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44827</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44868</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45552</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>44903</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>45531</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45700</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45282</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>44853</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45142</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45309</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>45273</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>45642</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>45350</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>45885</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>45885</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>45145</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>45888</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>45885</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45341</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45245</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45531</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>44907</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45133</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45352</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45481</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>44571</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45244</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45414</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45082</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45627</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>44907</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44900</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>45706</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>45912</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>45684</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>45777</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45460</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45166</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45556</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45803</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>44988</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45096</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45915</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45581</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44900</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45443</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44924</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45713</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45919</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45457</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>45552</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>45127</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45627</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>45924</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45555</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45268</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44664</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44958</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45730</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>45531</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45099</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45929</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>45631</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45593</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>45399</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45439</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>45394</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45328</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45763</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>45209</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>45493</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>45051</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44698</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45569</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45077</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>44923</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>45579</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>45938</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>45553</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>45938</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>45937</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45937</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>45811</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>45811</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45607</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45236</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44697</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>45156</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>45531</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45328</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>45569</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45763</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45237</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44853</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45831</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>45763</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>44900</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>45954</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45954</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45077</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44483</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45835</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>45961</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>45002</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45835</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>44987</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44749</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45627</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>45841</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>45841</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45841</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45841</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45841</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45664</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45664</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45841</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45971</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45972</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45974</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45764</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45699</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45972</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>44782</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45972</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>44746</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45720</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45741</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44756</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45530</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>44950</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45448</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45720</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45694</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45643</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45233</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>45405</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>46100</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>44978</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>44740</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45651</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45485</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>44858</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45049</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>46106</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>46111</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>44901</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45425</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45757</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44924</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45754</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45685</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>46100</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>46122</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45268</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>46134</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>44951</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>46134</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>44923</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45344</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45750</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>46009</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>44964</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44816</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44599</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>44900</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45460</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45246</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>46140</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>44901</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45076</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44937</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44972</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>44746</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45142</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45699</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45562</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>45349</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>44987</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44987</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>44956</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44792</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45625</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45324</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>45322</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>46057</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>46062</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>46146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>46152</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>46152</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>46152</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>46152</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>46152</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>46078</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>46152</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>46152</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>46152</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46085</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>45665</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45191</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>46168</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>46168</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45637</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44937</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>46206</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>46206</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>46206</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>46210</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46268</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>46268</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>46268</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>46268</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>46268</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>46268</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>46231</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>46275</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>46268</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>46282</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>46282</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>46288</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>46288</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>46288</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>46248</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>46248</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>46248</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>46251</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>46251</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>46296</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>46303</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45685</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45716</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45716</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>46045</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>

--- a/Översikt TÖREBODA.xlsx
+++ b/Översikt TÖREBODA.xlsx
@@ -601,7 +601,7 @@
         <v>45587</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44747</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45191</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>46288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44986</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>46150</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46085</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45552</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45552</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2073,7 +2073,7 @@
         <v>44608</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>45264</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>45727</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>46206</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>44985</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>44964</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>44610</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>44937</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>45729</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>45632</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45938</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>45621</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>45757</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>45166</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>45742</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>44608</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>46212</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>46274</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44690</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>44986</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44508</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44733</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>44740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>44818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44726</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44719</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44847</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44847</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44507</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         <v>44614</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>44719</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>44614</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5889,7 +5889,7 @@
         <v>44532</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>44579</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>44601</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>44531</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>44754</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44719</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>45056</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>45209</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>45096</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>44852</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
         <v>44741</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44818</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>45553</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>44894</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>44890</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45215</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>44860</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>45231</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7306,7 +7306,7 @@
         <v>45460</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7379,7 +7379,7 @@
         <v>45450</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         <v>45750</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         <v>45373</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>45443</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>45384</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45553</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>45369</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44978</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>44986</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45457</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>44827</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44827</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44868</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45552</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>44903</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>45531</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45700</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45282</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
         <v>44853</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45142</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45309</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>45273</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>45642</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9146,7 +9146,7 @@
         <v>45350</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>45885</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>45885</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>45145</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9438,7 +9438,7 @@
         <v>45888</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>45885</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9584,7 +9584,7 @@
         <v>45341</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>45245</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45531</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>44907</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9876,7 +9876,7 @@
         <v>45133</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45352</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10022,7 +10022,7 @@
         <v>45481</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10095,7 +10095,7 @@
         <v>44571</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45244</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>45414</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10314,7 +10314,7 @@
         <v>45082</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>45627</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>44907</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10533,7 +10533,7 @@
         <v>44900</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>45706</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>45912</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10752,7 +10752,7 @@
         <v>45684</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>45777</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         <v>45460</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>45166</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
         <v>45556</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>45803</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>44988</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>45096</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>45915</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>45581</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11497,7 +11497,7 @@
         <v>44900</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>45443</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>45727</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44924</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>45713</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11862,7 +11862,7 @@
         <v>45919</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45457</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12013,7 +12013,7 @@
         <v>45552</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>45127</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45627</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>45924</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12305,7 +12305,7 @@
         <v>45555</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45268</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12451,7 +12451,7 @@
         <v>44664</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12524,7 +12524,7 @@
         <v>44958</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>45730</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>45531</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>45099</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>45929</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12889,7 +12889,7 @@
         <v>45631</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>45593</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>45399</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13108,7 +13108,7 @@
         <v>45439</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13181,7 +13181,7 @@
         <v>45394</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>45145</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13327,7 +13327,7 @@
         <v>45328</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>45763</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>45209</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13551,7 +13551,7 @@
         <v>45493</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13624,7 +13624,7 @@
         <v>45051</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>44698</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13775,7 +13775,7 @@
         <v>45569</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45077</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13926,7 +13926,7 @@
         <v>44923</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>45579</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>45938</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14145,7 +14145,7 @@
         <v>45553</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>45938</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14291,7 +14291,7 @@
         <v>45937</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14369,7 +14369,7 @@
         <v>45937</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>45811</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>45811</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45607</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45236</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44697</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14812,7 +14812,7 @@
         <v>45156</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14885,7 +14885,7 @@
         <v>45531</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14958,7 +14958,7 @@
         <v>45328</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15031,7 +15031,7 @@
         <v>45569</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15104,7 +15104,7 @@
         <v>45763</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>45237</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>44853</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45831</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>45763</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>44900</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>45954</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15620,7 +15620,7 @@
         <v>45954</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15693,7 +15693,7 @@
         <v>45077</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>44483</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45835</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>45961</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>45002</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45835</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>44987</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>44749</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45627</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16360,7 +16360,7 @@
         <v>45841</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>45841</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>45841</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>45841</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45841</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16828,7 +16828,7 @@
         <v>45664</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16901,7 +16901,7 @@
         <v>45664</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>45841</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45971</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17125,7 +17125,7 @@
         <v>45972</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17198,7 +17198,7 @@
         <v>45974</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17271,7 +17271,7 @@
         <v>45764</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45699</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45972</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>44782</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45972</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>44746</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>45720</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45741</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>44756</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45530</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>44950</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45448</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18167,7 +18167,7 @@
         <v>45720</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18240,7 +18240,7 @@
         <v>45694</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45643</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45233</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>45405</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>46100</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18610,7 +18610,7 @@
         <v>44978</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>44740</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45651</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45485</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>44858</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>45049</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>46106</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>46111</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>44901</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45425</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>45757</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19418,7 +19418,7 @@
         <v>44924</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19491,7 +19491,7 @@
         <v>45754</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45685</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>46100</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>46122</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>45268</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19856,7 +19856,7 @@
         <v>46134</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>44951</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>46134</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20075,7 +20075,7 @@
         <v>44923</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45344</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45750</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20294,7 +20294,7 @@
         <v>46009</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>44964</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>44816</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>44599</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>44900</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20664,7 +20664,7 @@
         <v>45460</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
         <v>45246</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>46140</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20888,7 +20888,7 @@
         <v>44901</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45076</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>44937</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>44972</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
         <v>44746</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45142</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45699</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45562</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21477,7 +21477,7 @@
         <v>45349</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21550,7 +21550,7 @@
         <v>44987</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21623,7 +21623,7 @@
         <v>44987</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>44956</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>44792</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45625</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>45324</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>45322</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>46057</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>46062</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>46146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>46152</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>46152</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>46152</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>46152</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22572,7 +22572,7 @@
         <v>46152</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22645,7 +22645,7 @@
         <v>46078</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>46152</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>46152</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>46152</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46085</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>45665</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>45191</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>46168</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>46168</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>45637</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44937</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23463,7 +23463,7 @@
         <v>46206</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23541,7 +23541,7 @@
         <v>46206</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>46206</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>46210</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>46268</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>46268</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>46268</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>46268</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>46268</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>46268</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>46231</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>46275</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>46268</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>46282</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>46282</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>46288</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>46288</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>46288</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>46248</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>46248</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>46248</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>46251</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>46251</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>46296</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>46303</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45685</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45716</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45716</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>46045</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>

--- a/Översikt TÖREBODA.xlsx
+++ b/Översikt TÖREBODA.xlsx
@@ -601,7 +601,7 @@
         <v>45587</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44747</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45191</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>46288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44986</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45722</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46150</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44900</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46085</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45727</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45552</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45264</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45552</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>46206</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>45166</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>45621</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>44937</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>44985</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>45938</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44964</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44610</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>44608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>46212</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>46274</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>45729</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>45757</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>45742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44986</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44508</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44733</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>44740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>44818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44726</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44719</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44507</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44754</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44532</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>44601</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>44719</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>44847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>44847</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>44614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>44614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44531</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44852</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44818</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44853</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45237</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>45457</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45443</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44698</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45145</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45076</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45552</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45373</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45245</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45051</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44956</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45627</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>45699</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>44599</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45077</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45643</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44664</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45384</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>45344</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45166</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>44741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45651</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44816</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45309</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45664</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>45531</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45450</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45485</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45460</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45460</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>45282</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44988</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44987</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44987</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45099</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45369</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>44749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45457</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>45096</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>44890</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>44894</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44950</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44740</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45627</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45625</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45642</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45341</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45481</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>45350</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44978</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>44924</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45233</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44756</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45888</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45885</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>45885</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>44860</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>45885</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>45142</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44571</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>45579</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>46140</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>45399</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45552</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>44901</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44924</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>45684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45236</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>45915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45912</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>46146</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>45803</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>45919</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>45924</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44900</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44964</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45929</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45530</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>46152</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>46152</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>46152</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>46152</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>46152</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>46152</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>46152</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>45937</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>45938</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45938</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45328</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45937</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>46152</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>44978</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45244</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45443</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>44853</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45145</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>45665</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45553</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>45082</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45954</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45405</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45954</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>45352</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>45961</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>45268</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>45706</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>45971</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45553</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45972</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45972</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45972</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45974</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45349</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45555</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45664</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45637</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45460</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45754</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>45685</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45191</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>45273</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45531</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45096</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>46168</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>46168</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>44972</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45627</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>44792</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45156</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45322</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>46009</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45373</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>44900</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44868</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45049</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45750</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44937</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45694</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45133</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45056</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>44987</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>46057</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>46062</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44986</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45699</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45002</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>46078</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44958</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>44923</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>44923</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45556</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44746</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>46085</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45414</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>44907</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45562</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45700</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45127</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>46100</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>46106</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45763</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>46111</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>46100</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>46122</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>46134</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>46134</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45553</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>44900</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45231</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45750</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>46206</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>46206</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>46206</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>46210</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>45552</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45425</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45077</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>44903</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45448</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>44782</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>46275</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>46231</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45246</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45215</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45324</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>46282</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>46282</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45531</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45531</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>44827</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44827</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45209</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45268</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45328</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>46288</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>44907</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>46288</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>46288</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>46248</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>46248</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44900</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44951</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45757</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>46248</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45607</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45142</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46251</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44937</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>44697</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>46251</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>46296</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44746</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>45777</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45581</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45727</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>46303</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45713</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45730</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45493</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45394</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45439</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45209</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>45631</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45569</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45763</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>45593</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45811</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>46308</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>46308</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>46268</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>45811</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>46268</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>46268</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46268</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45569</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>46268</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>45763</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>46268</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>46268</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45831</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45835</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>45835</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45841</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45841</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45841</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45841</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>45841</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45841</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45841</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45764</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45720</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>45741</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45720</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45685</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45716</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>45716</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>46045</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>

--- a/Översikt TÖREBODA.xlsx
+++ b/Översikt TÖREBODA.xlsx
@@ -601,7 +601,7 @@
         <v>45587</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44747</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>45191</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
         <v>46288</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44986</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>45722</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>46150</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44900</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46085</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45727</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>45552</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         <v>45264</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>45552</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
         <v>44608</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>46206</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>45166</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         <v>45621</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>44937</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>44985</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>45938</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>44964</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>44610</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>44608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>46212</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>46274</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>45729</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         <v>45757</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>45742</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4116,7 +4116,7 @@
         <v>44986</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44509</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44508</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44503</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>44684</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>44733</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>44740</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>44818</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>44726</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44616</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>44719</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5144,7 +5144,7 @@
         <v>44614</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         <v>44546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44503</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5368,7 +5368,7 @@
         <v>44494</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>44507</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
         <v>44719</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44754</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>44532</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         <v>44601</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5811,7 +5811,7 @@
         <v>44719</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>44847</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>44847</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>44614</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
         <v>44614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6186,7 +6186,7 @@
         <v>44579</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6259,7 +6259,7 @@
         <v>44531</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>44852</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6405,7 +6405,7 @@
         <v>44818</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6483,7 +6483,7 @@
         <v>44853</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>44858</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45237</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>45457</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         <v>45443</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>44698</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>45145</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v>45076</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7077,7 +7077,7 @@
         <v>45552</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>45373</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>45245</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         <v>45051</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44956</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>45627</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7520,7 +7520,7 @@
         <v>45699</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>44599</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         <v>45077</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>45643</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44664</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>45384</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>45344</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8036,7 +8036,7 @@
         <v>45166</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8109,7 +8109,7 @@
         <v>44741</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45651</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>44816</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45309</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45664</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         <v>45531</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         <v>45450</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>45485</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8703,7 +8703,7 @@
         <v>45460</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         <v>45460</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>45282</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44988</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44987</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9068,7 +9068,7 @@
         <v>44987</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44901</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45099</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45369</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>44749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>45457</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>45096</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>44890</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>44894</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44950</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9813,7 +9813,7 @@
         <v>44740</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>45627</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45625</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45642</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45341</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>45481</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>45350</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44978</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>44924</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45233</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44756</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45888</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
         <v>45885</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>45885</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>44860</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>45885</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>45142</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11069,7 +11069,7 @@
         <v>44571</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>45579</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>46140</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>45399</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45552</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>44901</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>44924</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>45684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
         <v>45236</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11731,7 +11731,7 @@
         <v>45915</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45912</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11877,7 +11877,7 @@
         <v>46146</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>45803</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>45919</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12096,7 +12096,7 @@
         <v>45924</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44900</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44964</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45929</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45530</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>46152</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>46152</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>46152</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>46152</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>46152</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>46152</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>46152</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>45937</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>45938</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45938</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>45328</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45937</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>46152</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>44978</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>45244</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>45443</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>44853</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13717,7 +13717,7 @@
         <v>45145</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>45665</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>45553</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>45082</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>45954</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>45405</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45954</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>45352</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>45961</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>45268</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14447,7 +14447,7 @@
         <v>45706</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
         <v>45971</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14593,7 +14593,7 @@
         <v>45553</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14666,7 +14666,7 @@
         <v>45972</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>45972</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>45972</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>45974</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>45349</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>45555</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15114,7 +15114,7 @@
         <v>45664</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15187,7 +15187,7 @@
         <v>45637</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15260,7 +15260,7 @@
         <v>45460</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45754</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>45685</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45191</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15552,7 +15552,7 @@
         <v>45273</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45531</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45096</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>46168</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>46168</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>44972</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45627</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>44792</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45156</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45322</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>46009</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>45373</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>44900</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44868</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45049</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45750</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>44937</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45694</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45133</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45056</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>44987</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>46057</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>46062</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>44986</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45699</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45002</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>46078</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44958</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>44923</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>44923</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45556</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>44746</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>46085</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45414</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18054,7 +18054,7 @@
         <v>44907</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>45562</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18200,7 +18200,7 @@
         <v>45700</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>45127</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>46100</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>46106</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18492,7 +18492,7 @@
         <v>45763</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>46111</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>46100</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>46122</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>46134</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>46134</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45553</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>44900</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45231</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45750</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>46206</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>46206</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>46206</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>46210</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
         <v>45552</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45425</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45077</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>44903</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45448</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19914,7 +19914,7 @@
         <v>44782</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>46275</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>46231</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45246</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45215</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>45324</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>46282</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>46282</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45531</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45531</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>44827</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44827</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45209</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45268</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45328</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>46288</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>44907</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>46288</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>46288</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>46248</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>46248</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21467,7 +21467,7 @@
         <v>44900</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44951</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45757</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>46248</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45607</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45142</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46251</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44937</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>44697</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>46251</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22217,7 +22217,7 @@
         <v>46296</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>44746</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>45777</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>45581</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45727</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>46303</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>45713</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>45730</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>45493</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>45394</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45439</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45209</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>45631</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45569</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23249,7 +23249,7 @@
         <v>45763</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23327,7 +23327,7 @@
         <v>45593</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23400,7 +23400,7 @@
         <v>45811</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>46308</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>46308</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>46268</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>45811</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23770,7 +23770,7 @@
         <v>46268</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>46268</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>46268</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45569</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>46268</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24155,7 +24155,7 @@
         <v>45763</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24228,7 +24228,7 @@
         <v>46268</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24301,7 +24301,7 @@
         <v>46268</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45831</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24452,7 +24452,7 @@
         <v>45835</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>45835</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>45841</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>45841</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45841</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45841</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>45841</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24988,7 +24988,7 @@
         <v>45841</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45841</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45764</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45720</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25290,7 +25290,7 @@
         <v>45741</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45720</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45685</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45716</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25582,7 +25582,7 @@
         <v>45716</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25655,7 +25655,7 @@
         <v>46045</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>

--- a/Översikt TÖREBODA.xlsx
+++ b/Översikt TÖREBODA.xlsx
@@ -601,7 +601,7 @@
         <v>45587</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44747</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>46288</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45191</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44986</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>46150</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46085</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45552</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>46206</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>45727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>45552</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>45264</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>44608</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>45938</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>46212</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45729</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>45742</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>44964</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>44985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44610</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>44608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>46316</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>46274</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>44937</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>45632</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>45621</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45166</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44986</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44508</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>44503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>44684</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>44733</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>44740</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>44818</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44726</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44616</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>44719</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>44546</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44503</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>44494</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44507</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>44719</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44754</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>44532</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>44601</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>44847</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>44847</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>44614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44614</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44579</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44531</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>44951</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>44852</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>44818</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>45642</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45885</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>45885</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44923</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45888</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>45885</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45344</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45369</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44964</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44571</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44816</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45209</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44599</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44900</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>45460</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45246</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45912</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45684</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44901</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45076</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>45803</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44937</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>45915</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>45191</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>46168</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>46168</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>45919</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44972</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44746</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45142</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45924</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>45637</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>45699</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>45562</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45349</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>44987</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44987</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>45929</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44956</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>44792</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45938</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>45938</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45625</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>45324</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>45937</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>45937</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>45322</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>45056</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>45373</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>44741</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>44860</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45460</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45373</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44937</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45443</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>44894</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>44986</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>45457</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45954</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>45954</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>45750</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>45553</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>45961</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>44978</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44827</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44827</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>45971</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>45972</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45552</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44868</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45974</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>45700</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>45972</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45972</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>45552</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>45273</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>45350</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45245</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>45531</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>44907</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>44903</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>46206</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45531</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>46206</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>46206</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45352</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>45244</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>46210</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>45082</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>45282</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>44853</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45777</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>46231</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45581</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45727</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>46009</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45713</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>46282</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>46282</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>45730</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45631</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45593</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45439</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45394</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45763</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>45209</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45493</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>45569</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>46288</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>46057</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>46288</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>46288</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>46062</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45811</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45811</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>46248</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>46248</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>46248</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>46251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45341</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45569</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>46078</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>45763</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45831</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>46251</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>46085</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>46296</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45835</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45835</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45841</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45841</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45841</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>45841</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>45841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45841</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>45841</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>46100</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45764</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>46106</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45741</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>46111</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45481</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>46100</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>46122</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45414</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45720</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>46308</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>46308</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45627</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>44907</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>46134</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>44900</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>46134</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>44988</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>45750</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44900</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>44924</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>46268</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>46268</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>46268</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>46268</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>46140</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>46268</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45127</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>46268</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>46314</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>45720</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>46268</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>46316</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44958</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45531</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>45099</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>45399</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>46315</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>46316</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45051</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>44698</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>46317</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>46317</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>46317</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>46317</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>46303</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>44923</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>46317</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>46275</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>46317</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>46317</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>46146</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45579</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45553</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>46152</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>46152</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>46152</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>46152</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>46152</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>46152</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>46152</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>46152</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45665</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45328</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44853</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45077</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45002</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>44987</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>45627</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45664</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45664</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45699</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>44782</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44756</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45643</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45049</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>45425</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45757</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>44924</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45754</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>45096</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45553</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44890</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45215</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>45231</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45450</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45384</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45142</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45309</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45145</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45133</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45706</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45460</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45166</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45556</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45096</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45443</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45457</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>45552</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45627</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45555</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>45268</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44664</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45145</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>45328</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45077</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45607</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45236</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>44697</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45156</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45531</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45237</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>45763</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>44900</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44749</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>44746</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>45530</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44950</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45448</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45694</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45233</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45405</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44978</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>44740</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45651</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45485</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>44858</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44901</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45685</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45268</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45685</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45716</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45716</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>46045</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>

--- a/Översikt TÖREBODA.xlsx
+++ b/Översikt TÖREBODA.xlsx
@@ -601,7 +601,7 @@
         <v>45587</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>44747</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
         <v>46288</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45191</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44986</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>44900</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         <v>45722</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>46150</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
         <v>45713</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>46085</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45757</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>45552</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>46206</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>45727</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
         <v>45552</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>45264</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
         <v>44608</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>44837</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>45938</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>46212</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         <v>45729</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         <v>45757</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>45742</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>44964</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         <v>44985</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>44610</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
         <v>44608</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>46316</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>46274</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>44937</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>45632</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>45621</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45166</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>44690</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>44986</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>44509</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>44508</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44503</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>44503</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>44684</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
         <v>44733</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>44740</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         <v>44818</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>44726</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>44616</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>44719</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>44546</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44503</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>44494</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44507</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>44719</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44754</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>44532</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>44601</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44719</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5994,7 +5994,7 @@
         <v>44847</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>44847</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>44614</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44614</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6296,7 +6296,7 @@
         <v>44579</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>44531</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>44951</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>44852</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>44818</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>45642</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>45885</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>45885</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44923</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>45888</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>45885</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45344</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>45369</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44964</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44571</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44816</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>45209</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44599</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44900</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>45460</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45246</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>45912</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45684</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44901</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45076</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>45803</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44937</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>45915</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>45191</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>46168</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>46168</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         <v>45919</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>44972</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44746</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45142</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>45924</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>45637</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>45699</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>45562</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>45349</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>44987</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>44987</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>45929</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44956</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>44792</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45938</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>45938</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9752,7 +9752,7 @@
         <v>45625</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>45324</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>45937</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         <v>45937</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>45322</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>45056</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>45373</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>44741</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>44860</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45460</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45373</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         <v>44937</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>45443</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
         <v>44894</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>44986</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>45457</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45954</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>45954</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>45750</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11164,7 +11164,7 @@
         <v>45553</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>45961</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11310,7 +11310,7 @@
         <v>44978</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>44827</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44827</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11529,7 +11529,7 @@
         <v>45971</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>45972</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>45552</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>44868</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45974</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>45700</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11967,7 +11967,7 @@
         <v>45972</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45972</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>45552</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>45273</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>45350</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45245</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>45531</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>44907</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>44903</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>46206</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45531</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>46206</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>46206</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45352</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>45244</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13087,7 +13087,7 @@
         <v>46210</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>45082</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>45282</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>44853</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         <v>45777</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>46231</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45581</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>45727</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>46009</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45713</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13837,7 +13837,7 @@
         <v>46282</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>46282</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
         <v>45730</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>45631</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45593</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>45439</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45394</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45763</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>45209</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45493</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>45569</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>46288</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14723,7 +14723,7 @@
         <v>46057</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>46288</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>46288</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>46062</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15015,7 +15015,7 @@
         <v>45811</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>45811</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>46248</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>46248</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>46248</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>46251</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45341</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45569</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>46078</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>45763</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45831</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>46251</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>46085</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>46296</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45835</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>45835</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>45841</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>45841</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45841</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>45841</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>45841</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>45841</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>45841</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>46100</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45764</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16900,7 +16900,7 @@
         <v>46106</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16973,7 +16973,7 @@
         <v>45741</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         <v>46111</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17119,7 +17119,7 @@
         <v>45481</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17192,7 +17192,7 @@
         <v>46100</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>46122</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45414</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17411,7 +17411,7 @@
         <v>45720</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>46308</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>46308</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45627</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>44907</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>46134</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17849,7 +17849,7 @@
         <v>44900</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17922,7 +17922,7 @@
         <v>46134</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>44988</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18068,7 +18068,7 @@
         <v>45750</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44900</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>44924</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>46268</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>46268</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>46268</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>46268</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>46140</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>46268</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45127</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>46268</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>46314</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>45720</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>46268</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>46316</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44958</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45531</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>45099</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>45399</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>46315</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>46316</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45051</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>44698</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>46317</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>46317</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>46317</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>46317</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>46303</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>44923</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>46317</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>46275</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20406,7 +20406,7 @@
         <v>46317</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20484,7 +20484,7 @@
         <v>46317</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>46146</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45579</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45553</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>46152</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>46152</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>46152</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>46152</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>46152</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>46152</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>46152</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21292,7 +21292,7 @@
         <v>46152</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45665</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>45328</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21511,7 +21511,7 @@
         <v>44853</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45077</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21667,7 +21667,7 @@
         <v>45002</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>44987</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>45627</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21886,7 +21886,7 @@
         <v>45664</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21959,7 +21959,7 @@
         <v>45664</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>45699</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22105,7 +22105,7 @@
         <v>44782</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>44756</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45643</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>45049</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>45425</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
         <v>45757</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>44924</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45754</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>45096</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45553</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44890</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22923,7 +22923,7 @@
         <v>45215</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22996,7 +22996,7 @@
         <v>45231</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23074,7 +23074,7 @@
         <v>45450</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45384</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45142</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45309</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23371,7 +23371,7 @@
         <v>45145</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>45133</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45706</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23590,7 +23590,7 @@
         <v>45460</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>45166</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23736,7 +23736,7 @@
         <v>45556</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23809,7 +23809,7 @@
         <v>45096</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23887,7 +23887,7 @@
         <v>45443</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23960,7 +23960,7 @@
         <v>45457</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24038,7 +24038,7 @@
         <v>45552</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>45627</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24184,7 +24184,7 @@
         <v>45555</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>45268</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44664</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45145</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>45328</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45077</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24627,7 +24627,7 @@
         <v>45607</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>45236</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24773,7 +24773,7 @@
         <v>44697</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>45156</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>45531</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24992,7 +24992,7 @@
         <v>45237</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>45763</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>44900</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44749</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>44746</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25357,7 +25357,7 @@
         <v>45530</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25430,7 +25430,7 @@
         <v>44950</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25503,7 +25503,7 @@
         <v>45448</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25581,7 +25581,7 @@
         <v>45694</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25654,7 +25654,7 @@
         <v>45233</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25732,7 +25732,7 @@
         <v>45405</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25805,7 +25805,7 @@
         <v>44978</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25878,7 +25878,7 @@
         <v>44740</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25951,7 +25951,7 @@
         <v>45651</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26024,7 +26024,7 @@
         <v>45485</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>44858</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26175,7 +26175,7 @@
         <v>44901</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45685</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45268</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26394,7 +26394,7 @@
         <v>45685</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26467,7 +26467,7 @@
         <v>45716</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26540,7 +26540,7 @@
         <v>45716</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>46045</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
